--- a/research/traditional_assets/database/data/egypt/egypt_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_oilfield_svcs_equip.xlsx
@@ -588,118 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.151</v>
+        <v>-0.15</v>
       </c>
       <c r="G2">
-        <v>-0.4341147938561035</v>
+        <v>-0.03525835866261398</v>
       </c>
       <c r="H2">
-        <v>-0.4341147938561035</v>
+        <v>-0.03525835866261398</v>
       </c>
       <c r="I2">
-        <v>-0.6523848019401779</v>
+        <v>-0.3424518743667679</v>
       </c>
       <c r="J2">
-        <v>-0.6523848019401779</v>
+        <v>-0.3424518743667679</v>
       </c>
       <c r="K2">
-        <v>-94.09999999999999</v>
+        <v>-69.2</v>
       </c>
       <c r="L2">
-        <v>-0.7607113985448666</v>
+        <v>-0.701114488348531</v>
       </c>
       <c r="M2">
-        <v>0.151</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.002451298701298701</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.001604675876726886</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>0.151</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.002451298701298701</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.001604675876726886</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>10.1</v>
+        <v>3.25</v>
       </c>
       <c r="V2">
-        <v>0.1639610389610389</v>
+        <v>0.06063432835820896</v>
       </c>
       <c r="W2">
-        <v>-0.3041370394311571</v>
+        <v>-0.299696838458207</v>
       </c>
       <c r="X2">
-        <v>0.6718260237662461</v>
+        <v>1.088114672035709</v>
       </c>
       <c r="Y2">
-        <v>-0.9759630631974032</v>
+        <v>-1.387811510493916</v>
       </c>
       <c r="Z2">
-        <v>0.2327243993753881</v>
+        <v>0.1512272852633837</v>
       </c>
       <c r="AA2">
-        <v>-0.1518258611931594</v>
+        <v>-0.05178806729384365</v>
       </c>
       <c r="AB2">
-        <v>0.1299074704917994</v>
+        <v>0.2024098128631647</v>
       </c>
       <c r="AC2">
-        <v>-0.2817333316849588</v>
+        <v>-0.2541978801570084</v>
       </c>
       <c r="AD2">
-        <v>442</v>
+        <v>441.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>442</v>
+        <v>441.1</v>
       </c>
       <c r="AG2">
-        <v>431.9</v>
+        <v>437.85</v>
       </c>
       <c r="AH2">
-        <v>0.8776806989674344</v>
+        <v>0.89165150596321</v>
       </c>
       <c r="AI2">
-        <v>0.6711205587610082</v>
+        <v>0.7202808621815806</v>
       </c>
       <c r="AJ2">
-        <v>0.8751773049645389</v>
+        <v>0.8909349882999288</v>
       </c>
       <c r="AK2">
-        <v>0.6659984579799537</v>
+        <v>0.7187884757448904</v>
       </c>
       <c r="AL2">
-        <v>24.3</v>
+        <v>19.1</v>
       </c>
       <c r="AM2">
-        <v>23.743</v>
+        <v>18.97</v>
       </c>
       <c r="AN2">
-        <v>-9.692982456140351</v>
+        <v>-1246.045197740113</v>
       </c>
       <c r="AO2">
-        <v>-3.320987654320988</v>
+        <v>-1.769633507853403</v>
       </c>
       <c r="AP2">
-        <v>-9.471491228070175</v>
+        <v>-1236.864406779661</v>
       </c>
       <c r="AQ2">
-        <v>-3.398896516868129</v>
+        <v>-1.781760674749604</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +716,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.151</v>
+        <v>-0.15</v>
       </c>
       <c r="G3">
-        <v>-0.4341147938561035</v>
+        <v>-0.03525835866261398</v>
       </c>
       <c r="H3">
-        <v>-0.4341147938561035</v>
+        <v>-0.03525835866261398</v>
       </c>
       <c r="I3">
-        <v>-0.6523848019401779</v>
+        <v>-0.3424518743667679</v>
       </c>
       <c r="J3">
-        <v>-0.6523848019401779</v>
+        <v>-0.3424518743667679</v>
       </c>
       <c r="K3">
-        <v>-94.09999999999999</v>
+        <v>-69.2</v>
       </c>
       <c r="L3">
-        <v>-0.7607113985448666</v>
+        <v>-0.701114488348531</v>
       </c>
       <c r="M3">
-        <v>0.151</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.002451298701298701</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.001604675876726886</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0.151</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.002451298701298701</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.001604675876726886</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>10.1</v>
+        <v>3.25</v>
       </c>
       <c r="V3">
-        <v>0.1639610389610389</v>
+        <v>0.06063432835820896</v>
       </c>
       <c r="W3">
-        <v>-0.3041370394311571</v>
+        <v>-0.299696838458207</v>
       </c>
       <c r="X3">
-        <v>0.6718260237662461</v>
+        <v>1.088114672035709</v>
       </c>
       <c r="Y3">
-        <v>-0.9759630631974032</v>
+        <v>-1.387811510493916</v>
       </c>
       <c r="Z3">
-        <v>0.2327243993753881</v>
+        <v>0.1512272852633837</v>
       </c>
       <c r="AA3">
-        <v>-0.1518258611931594</v>
+        <v>-0.05178806729384365</v>
       </c>
       <c r="AB3">
-        <v>0.1299074704917994</v>
+        <v>0.2024098128631647</v>
       </c>
       <c r="AC3">
-        <v>-0.2817333316849588</v>
+        <v>-0.2541978801570084</v>
       </c>
       <c r="AD3">
-        <v>442</v>
+        <v>441.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>442</v>
+        <v>441.1</v>
       </c>
       <c r="AG3">
-        <v>431.9</v>
+        <v>437.85</v>
       </c>
       <c r="AH3">
-        <v>0.8776806989674344</v>
+        <v>0.89165150596321</v>
       </c>
       <c r="AI3">
-        <v>0.6711205587610082</v>
+        <v>0.7202808621815806</v>
       </c>
       <c r="AJ3">
-        <v>0.8751773049645389</v>
+        <v>0.8909349882999288</v>
       </c>
       <c r="AK3">
-        <v>0.6659984579799537</v>
+        <v>0.7187884757448904</v>
       </c>
       <c r="AL3">
-        <v>24.3</v>
+        <v>19.1</v>
       </c>
       <c r="AM3">
-        <v>23.743</v>
+        <v>18.97</v>
       </c>
       <c r="AN3">
-        <v>-9.692982456140351</v>
+        <v>-1246.045197740113</v>
       </c>
       <c r="AO3">
-        <v>-3.320987654320988</v>
+        <v>-1.769633507853403</v>
       </c>
       <c r="AP3">
-        <v>-9.471491228070175</v>
+        <v>-1236.864406779661</v>
       </c>
       <c r="AQ3">
-        <v>-3.398896516868129</v>
+        <v>-1.781760674749604</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/egypt/egypt_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_oilfield_svcs_equip.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.15</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="G2">
-        <v>-0.03525835866261398</v>
+        <v>-0.4264055590650663</v>
       </c>
       <c r="H2">
-        <v>-0.03525835866261398</v>
+        <v>-0.4264055590650663</v>
       </c>
       <c r="I2">
-        <v>-0.3424518743667679</v>
+        <v>-0.2192040429564119</v>
       </c>
       <c r="J2">
-        <v>-0.3424518743667679</v>
+        <v>-0.2192040429564119</v>
       </c>
       <c r="K2">
-        <v>-69.2</v>
+        <v>-48.6</v>
       </c>
       <c r="L2">
-        <v>-0.701114488348531</v>
+        <v>-0.3070120025268477</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.25</v>
+        <v>14</v>
       </c>
       <c r="V2">
-        <v>0.06063432835820896</v>
+        <v>0.1804123711340206</v>
       </c>
       <c r="W2">
-        <v>-0.299696838458207</v>
+        <v>-0.3001852995676343</v>
       </c>
       <c r="X2">
-        <v>1.088114672035709</v>
+        <v>0.7442928441565548</v>
       </c>
       <c r="Y2">
-        <v>-1.387811510493916</v>
+        <v>-1.044478143724189</v>
       </c>
       <c r="Z2">
-        <v>0.1512272852633837</v>
+        <v>0.2683460188842366</v>
       </c>
       <c r="AA2">
-        <v>-0.05178806729384365</v>
+        <v>-0.05882253225068231</v>
       </c>
       <c r="AB2">
-        <v>0.2024098128631647</v>
+        <v>0.1940407442327765</v>
       </c>
       <c r="AC2">
-        <v>-0.2541978801570084</v>
+        <v>-0.2528632764834588</v>
       </c>
       <c r="AD2">
-        <v>441.1</v>
+        <v>467.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>441.1</v>
+        <v>467.6</v>
       </c>
       <c r="AG2">
-        <v>437.85</v>
+        <v>453.6</v>
       </c>
       <c r="AH2">
-        <v>0.89165150596321</v>
+        <v>0.8576669112252384</v>
       </c>
       <c r="AI2">
-        <v>0.7202808621815806</v>
+        <v>1.103871576959396</v>
       </c>
       <c r="AJ2">
-        <v>0.8909349882999288</v>
+        <v>0.8539156626506024</v>
       </c>
       <c r="AK2">
-        <v>0.7187884757448904</v>
+        <v>1.107421875</v>
       </c>
       <c r="AL2">
-        <v>19.1</v>
+        <v>30.8</v>
       </c>
       <c r="AM2">
-        <v>18.97</v>
+        <v>30.074</v>
       </c>
       <c r="AN2">
-        <v>-1246.045197740113</v>
+        <v>-34.38235294117647</v>
       </c>
       <c r="AO2">
-        <v>-1.769633507853403</v>
+        <v>-1.126623376623377</v>
       </c>
       <c r="AP2">
-        <v>-1236.864406779661</v>
+        <v>-33.35294117647059</v>
       </c>
       <c r="AQ2">
-        <v>-1.781760674749604</v>
+        <v>-1.153820575912749</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.15</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="G3">
-        <v>-0.03525835866261398</v>
+        <v>-0.4264055590650663</v>
       </c>
       <c r="H3">
-        <v>-0.03525835866261398</v>
+        <v>-0.4264055590650663</v>
       </c>
       <c r="I3">
-        <v>-0.3424518743667679</v>
+        <v>-0.2192040429564119</v>
       </c>
       <c r="J3">
-        <v>-0.3424518743667679</v>
+        <v>-0.2192040429564119</v>
       </c>
       <c r="K3">
-        <v>-69.2</v>
+        <v>-48.6</v>
       </c>
       <c r="L3">
-        <v>-0.701114488348531</v>
+        <v>-0.3070120025268477</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.25</v>
+        <v>14</v>
       </c>
       <c r="V3">
-        <v>0.06063432835820896</v>
+        <v>0.1804123711340206</v>
       </c>
       <c r="W3">
-        <v>-0.299696838458207</v>
+        <v>-0.3001852995676343</v>
       </c>
       <c r="X3">
-        <v>1.088114672035709</v>
+        <v>0.7442928441565548</v>
       </c>
       <c r="Y3">
-        <v>-1.387811510493916</v>
+        <v>-1.044478143724189</v>
       </c>
       <c r="Z3">
-        <v>0.1512272852633837</v>
+        <v>0.2683460188842366</v>
       </c>
       <c r="AA3">
-        <v>-0.05178806729384365</v>
+        <v>-0.05882253225068231</v>
       </c>
       <c r="AB3">
-        <v>0.2024098128631647</v>
+        <v>0.1940407442327765</v>
       </c>
       <c r="AC3">
-        <v>-0.2541978801570084</v>
+        <v>-0.2528632764834588</v>
       </c>
       <c r="AD3">
-        <v>441.1</v>
+        <v>467.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>441.1</v>
+        <v>467.6</v>
       </c>
       <c r="AG3">
-        <v>437.85</v>
+        <v>453.6</v>
       </c>
       <c r="AH3">
-        <v>0.89165150596321</v>
+        <v>0.8576669112252384</v>
       </c>
       <c r="AI3">
-        <v>0.7202808621815806</v>
+        <v>1.103871576959396</v>
       </c>
       <c r="AJ3">
-        <v>0.8909349882999288</v>
+        <v>0.8539156626506024</v>
       </c>
       <c r="AK3">
-        <v>0.7187884757448904</v>
+        <v>1.107421875</v>
       </c>
       <c r="AL3">
-        <v>19.1</v>
+        <v>30.8</v>
       </c>
       <c r="AM3">
-        <v>18.97</v>
+        <v>30.074</v>
       </c>
       <c r="AN3">
-        <v>-1246.045197740113</v>
+        <v>-34.38235294117647</v>
       </c>
       <c r="AO3">
-        <v>-1.769633507853403</v>
+        <v>-1.126623376623377</v>
       </c>
       <c r="AP3">
-        <v>-1236.864406779661</v>
+        <v>-33.35294117647059</v>
       </c>
       <c r="AQ3">
-        <v>-1.781760674749604</v>
+        <v>-1.153820575912749</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/egypt/egypt_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_oilfield_svcs_equip.xlsx
@@ -1263,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1400,22 +1400,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1604381941031026</v>
+        <v>0.1601120831663706</v>
       </c>
       <c r="C2">
-        <v>621.8023505511533</v>
+        <v>618.2267473346303</v>
       </c>
       <c r="D2">
-        <v>602.7023505511532</v>
+        <v>604.4217473346303</v>
       </c>
       <c r="E2">
-        <v>-356.9</v>
+        <v>-351.605</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.295</v>
       </c>
       <c r="G2">
         <v>19.1</v>
@@ -1436,28 +1436,28 @@
         <v>96.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2663385</v>
       </c>
       <c r="N2">
-        <v>96.2</v>
+        <v>95.9336615</v>
       </c>
       <c r="O2">
-        <v>21.645</v>
+        <v>21.5850738375</v>
       </c>
       <c r="P2">
-        <v>74.55500000000001</v>
+        <v>74.34858766249999</v>
       </c>
       <c r="Q2">
-        <v>95.855</v>
+        <v>95.64858766249999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1604381941031026</v>
+        <v>0.1613356143094652</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751836</v>
+        <v>0.8055654338116054</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>361.1944949753791</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1482,22 +1482,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1601120831663706</v>
+        <v>0.1597859722296386</v>
       </c>
       <c r="C3">
-        <v>618.2267473346303</v>
+        <v>614.6609824181139</v>
       </c>
       <c r="D3">
-        <v>604.4217473346303</v>
+        <v>606.1509824181139</v>
       </c>
       <c r="E3">
-        <v>-351.605</v>
+        <v>-346.31</v>
       </c>
       <c r="F3">
-        <v>5.295</v>
+        <v>10.59</v>
       </c>
       <c r="G3">
         <v>19.1</v>
@@ -1518,28 +1518,28 @@
         <v>96.2</v>
       </c>
       <c r="M3">
-        <v>0.2663385</v>
+        <v>0.532677</v>
       </c>
       <c r="N3">
-        <v>95.9336615</v>
+        <v>95.667323</v>
       </c>
       <c r="O3">
-        <v>21.5850738375</v>
+        <v>21.525147675</v>
       </c>
       <c r="P3">
-        <v>74.34858766249999</v>
+        <v>74.142175325</v>
       </c>
       <c r="Q3">
-        <v>95.64858766249999</v>
+        <v>95.44217532499999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1613356143094652</v>
+        <v>0.1622513492139169</v>
       </c>
       <c r="T3">
-        <v>0.8055654338116054</v>
+        <v>0.8119503428283624</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>361.1944949753791</v>
+        <v>180.5972474876895</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1564,22 +1564,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1597859722296386</v>
+        <v>0.1594598612929066</v>
       </c>
       <c r="C4">
-        <v>614.6609824181139</v>
+        <v>611.1051404852523</v>
       </c>
       <c r="D4">
-        <v>606.1509824181139</v>
+        <v>607.8901404852522</v>
       </c>
       <c r="E4">
-        <v>-346.31</v>
+        <v>-341.015</v>
       </c>
       <c r="F4">
-        <v>10.59</v>
+        <v>15.885</v>
       </c>
       <c r="G4">
         <v>19.1</v>
@@ -1600,28 +1600,28 @@
         <v>96.2</v>
       </c>
       <c r="M4">
-        <v>0.532677</v>
+        <v>0.7990155</v>
       </c>
       <c r="N4">
-        <v>95.667323</v>
+        <v>95.40098450000001</v>
       </c>
       <c r="O4">
-        <v>21.525147675</v>
+        <v>21.4652215125</v>
       </c>
       <c r="P4">
-        <v>74.142175325</v>
+        <v>73.9357629875</v>
       </c>
       <c r="Q4">
-        <v>95.44217532499999</v>
+        <v>95.2357629875</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1622513492139169</v>
+        <v>0.1631859652504192</v>
       </c>
       <c r="T4">
-        <v>0.8119503428283624</v>
+        <v>0.8184668994537124</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>180.5972474876895</v>
+        <v>120.398164991793</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1646,22 +1646,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1594598612929066</v>
+        <v>0.1591337503561746</v>
       </c>
       <c r="C5">
-        <v>611.1051404852523</v>
+        <v>607.5593071943813</v>
       </c>
       <c r="D5">
-        <v>607.8901404852522</v>
+        <v>609.6393071943812</v>
       </c>
       <c r="E5">
-        <v>-341.015</v>
+        <v>-335.72</v>
       </c>
       <c r="F5">
-        <v>15.885</v>
+        <v>21.18</v>
       </c>
       <c r="G5">
         <v>19.1</v>
@@ -1682,28 +1682,28 @@
         <v>96.2</v>
       </c>
       <c r="M5">
-        <v>0.7990155</v>
+        <v>1.065354</v>
       </c>
       <c r="N5">
-        <v>95.40098450000001</v>
+        <v>95.134646</v>
       </c>
       <c r="O5">
-        <v>21.4652215125</v>
+        <v>21.40529535</v>
       </c>
       <c r="P5">
-        <v>73.9357629875</v>
+        <v>73.72935065</v>
       </c>
       <c r="Q5">
-        <v>95.2357629875</v>
+        <v>95.02935065</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1631859652504192</v>
+        <v>0.1641400524543486</v>
       </c>
       <c r="T5">
-        <v>0.8184668994537124</v>
+        <v>0.8251192176754238</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>120.398164991793</v>
+        <v>90.29862374384479</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1728,22 +1728,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1591337503561746</v>
+        <v>0.1588076394194426</v>
       </c>
       <c r="C6">
-        <v>607.5593071943813</v>
+        <v>604.0235691925892</v>
       </c>
       <c r="D6">
-        <v>609.6393071943812</v>
+        <v>611.3985691925892</v>
       </c>
       <c r="E6">
-        <v>-335.72</v>
+        <v>-330.425</v>
       </c>
       <c r="F6">
-        <v>21.18</v>
+        <v>26.475</v>
       </c>
       <c r="G6">
         <v>19.1</v>
@@ -1764,28 +1764,28 @@
         <v>96.2</v>
       </c>
       <c r="M6">
-        <v>1.065354</v>
+        <v>1.3316925</v>
       </c>
       <c r="N6">
-        <v>95.134646</v>
+        <v>94.8683075</v>
       </c>
       <c r="O6">
-        <v>21.40529535</v>
+        <v>21.3453691875</v>
       </c>
       <c r="P6">
-        <v>73.72935065</v>
+        <v>73.5229383125</v>
       </c>
       <c r="Q6">
-        <v>95.02935065</v>
+        <v>94.8229383125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1641400524543486</v>
+        <v>0.1651142257046765</v>
       </c>
       <c r="T6">
-        <v>0.8251192176754238</v>
+        <v>0.8319115847018028</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>90.29862374384479</v>
+        <v>72.23889899507581</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1810,22 +1810,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1588076394194426</v>
+        <v>0.1584815284827107</v>
       </c>
       <c r="C7">
-        <v>604.0235691925892</v>
+        <v>600.4980141300225</v>
       </c>
       <c r="D7">
-        <v>611.3985691925892</v>
+        <v>613.1680141300225</v>
       </c>
       <c r="E7">
-        <v>-330.425</v>
+        <v>-325.13</v>
       </c>
       <c r="F7">
-        <v>26.475</v>
+        <v>31.77</v>
       </c>
       <c r="G7">
         <v>19.1</v>
@@ -1846,28 +1846,28 @@
         <v>96.2</v>
       </c>
       <c r="M7">
-        <v>1.3316925</v>
+        <v>1.598031</v>
       </c>
       <c r="N7">
-        <v>94.8683075</v>
+        <v>94.601969</v>
       </c>
       <c r="O7">
-        <v>21.3453691875</v>
+        <v>21.285443025</v>
       </c>
       <c r="P7">
-        <v>73.5229383125</v>
+        <v>73.31652597499999</v>
       </c>
       <c r="Q7">
-        <v>94.8229383125</v>
+        <v>94.61652597499999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1651142257046765</v>
+        <v>0.1661091260454369</v>
       </c>
       <c r="T7">
-        <v>0.8319115847018028</v>
+        <v>0.8388484701755516</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>72.23889899507581</v>
+        <v>60.19908249589651</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1892,22 +1892,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1584815284827107</v>
+        <v>0.1581554175459787</v>
       </c>
       <c r="C8">
-        <v>600.4980141300225</v>
+        <v>596.9827306744446</v>
       </c>
       <c r="D8">
-        <v>613.1680141300225</v>
+        <v>614.9477306744445</v>
       </c>
       <c r="E8">
-        <v>-325.13</v>
+        <v>-319.835</v>
       </c>
       <c r="F8">
-        <v>31.77</v>
+        <v>37.065</v>
       </c>
       <c r="G8">
         <v>19.1</v>
@@ -1928,28 +1928,28 @@
         <v>96.2</v>
       </c>
       <c r="M8">
-        <v>1.598031</v>
+        <v>1.8643695</v>
       </c>
       <c r="N8">
-        <v>94.601969</v>
+        <v>94.33563050000001</v>
       </c>
       <c r="O8">
-        <v>21.285443025</v>
+        <v>21.2255168625</v>
       </c>
       <c r="P8">
-        <v>73.31652597499999</v>
+        <v>73.11011363750001</v>
       </c>
       <c r="Q8">
-        <v>94.61652597499999</v>
+        <v>94.4101136375</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1661091260454369</v>
+        <v>0.1671254220924502</v>
       </c>
       <c r="T8">
-        <v>0.8388484701755516</v>
+        <v>0.8459345359820692</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>60.19908249589651</v>
+        <v>51.59921356791131</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1974,22 +1974,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1581554175459787</v>
+        <v>0.1578293066092467</v>
       </c>
       <c r="C9">
-        <v>596.9827306744446</v>
+        <v>593.4778085260458</v>
       </c>
       <c r="D9">
-        <v>614.9477306744446</v>
+        <v>616.7378085260458</v>
       </c>
       <c r="E9">
-        <v>-319.835</v>
+        <v>-314.54</v>
       </c>
       <c r="F9">
-        <v>37.065</v>
+        <v>42.36</v>
       </c>
       <c r="G9">
         <v>19.1</v>
@@ -2010,28 +2010,28 @@
         <v>96.2</v>
       </c>
       <c r="M9">
-        <v>1.8643695</v>
+        <v>2.130708</v>
       </c>
       <c r="N9">
-        <v>94.33563050000001</v>
+        <v>94.069292</v>
       </c>
       <c r="O9">
-        <v>21.2255168625</v>
+        <v>21.1655907</v>
       </c>
       <c r="P9">
-        <v>73.11011363750001</v>
+        <v>72.90370129999999</v>
       </c>
       <c r="Q9">
-        <v>94.4101136375</v>
+        <v>94.20370129999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1671254220924502</v>
+        <v>0.1681638115317899</v>
       </c>
       <c r="T9">
-        <v>0.8459345359820692</v>
+        <v>0.8531746466974242</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>51.59921356791129</v>
+        <v>45.14931187192239</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2056,22 +2056,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1578293066092467</v>
+        <v>0.1575031956725147</v>
       </c>
       <c r="C10">
-        <v>593.4778085260458</v>
+        <v>589.9833384325143</v>
       </c>
       <c r="D10">
-        <v>616.7378085260458</v>
+        <v>618.5383384325143</v>
       </c>
       <c r="E10">
-        <v>-314.54</v>
+        <v>-309.245</v>
       </c>
       <c r="F10">
-        <v>42.36</v>
+        <v>47.655</v>
       </c>
       <c r="G10">
         <v>19.1</v>
@@ -2092,28 +2092,28 @@
         <v>96.2</v>
       </c>
       <c r="M10">
-        <v>2.130708</v>
+        <v>2.3970465</v>
       </c>
       <c r="N10">
-        <v>94.069292</v>
+        <v>93.8029535</v>
       </c>
       <c r="O10">
-        <v>21.1655907</v>
+        <v>21.1056645375</v>
       </c>
       <c r="P10">
-        <v>72.90370129999999</v>
+        <v>72.6972889625</v>
       </c>
       <c r="Q10">
-        <v>94.20370129999999</v>
+        <v>93.99728896249999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1681638115317899</v>
+        <v>0.1692250227170491</v>
       </c>
       <c r="T10">
-        <v>0.8531746466974242</v>
+        <v>0.8605738807252045</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>45.14931187192239</v>
+        <v>40.13272166393101</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2138,22 +2138,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1575031956725147</v>
+        <v>0.1571770847357827</v>
       </c>
       <c r="C11">
-        <v>589.9833384325143</v>
+        <v>586.4994122043712</v>
       </c>
       <c r="D11">
-        <v>618.5383384325143</v>
+        <v>620.3494122043712</v>
       </c>
       <c r="E11">
-        <v>-309.245</v>
+        <v>-303.95</v>
       </c>
       <c r="F11">
-        <v>47.655</v>
+        <v>52.95</v>
       </c>
       <c r="G11">
         <v>19.1</v>
@@ -2174,28 +2174,28 @@
         <v>96.2</v>
       </c>
       <c r="M11">
-        <v>2.3970465</v>
+        <v>2.663384999999999</v>
       </c>
       <c r="N11">
-        <v>93.8029535</v>
+        <v>93.536615</v>
       </c>
       <c r="O11">
-        <v>21.1056645375</v>
+        <v>21.045738375</v>
       </c>
       <c r="P11">
-        <v>72.6972889625</v>
+        <v>72.490876625</v>
       </c>
       <c r="Q11">
-        <v>93.99728896249999</v>
+        <v>93.790876625</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1692250227170491</v>
+        <v>0.1703098163730919</v>
       </c>
       <c r="T11">
-        <v>0.8605738807252045</v>
+        <v>0.8681375421758243</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>40.13272166393101</v>
+        <v>36.11944949753791</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2220,22 +2220,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1571770847357827</v>
+        <v>0.1568509737990507</v>
       </c>
       <c r="C12">
-        <v>586.4994122043712</v>
+        <v>583.0261227305768</v>
       </c>
       <c r="D12">
-        <v>620.3494122043712</v>
+        <v>622.1711227305768</v>
       </c>
       <c r="E12">
-        <v>-303.95</v>
+        <v>-298.655</v>
       </c>
       <c r="F12">
-        <v>52.95</v>
+        <v>58.245</v>
       </c>
       <c r="G12">
         <v>19.1</v>
@@ -2256,28 +2256,28 @@
         <v>96.2</v>
       </c>
       <c r="M12">
-        <v>2.663385</v>
+        <v>2.9297235</v>
       </c>
       <c r="N12">
-        <v>93.536615</v>
+        <v>93.27027650000001</v>
       </c>
       <c r="O12">
-        <v>21.045738375</v>
+        <v>20.9858122125</v>
       </c>
       <c r="P12">
-        <v>72.490876625</v>
+        <v>72.28446428750001</v>
       </c>
       <c r="Q12">
-        <v>93.790876625</v>
+        <v>93.58446428750001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1703098163730919</v>
+        <v>0.1714189874146638</v>
       </c>
       <c r="T12">
-        <v>0.8681375421758243</v>
+        <v>0.8758711735466828</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>36.11944949753791</v>
+        <v>32.83586317957992</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2302,22 +2302,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1568509737990507</v>
+        <v>0.1565248628623188</v>
       </c>
       <c r="C13">
-        <v>583.0261227305768</v>
+        <v>579.5635639944106</v>
       </c>
       <c r="D13">
-        <v>622.1711227305768</v>
+        <v>624.0035639944106</v>
       </c>
       <c r="E13">
-        <v>-298.655</v>
+        <v>-293.36</v>
       </c>
       <c r="F13">
-        <v>58.245</v>
+        <v>63.54</v>
       </c>
       <c r="G13">
         <v>19.1</v>
@@ -2338,28 +2338,28 @@
         <v>96.2</v>
       </c>
       <c r="M13">
-        <v>2.9297235</v>
+        <v>3.196062</v>
       </c>
       <c r="N13">
-        <v>93.27027650000001</v>
+        <v>93.00393800000001</v>
       </c>
       <c r="O13">
-        <v>20.9858122125</v>
+        <v>20.92588605</v>
       </c>
       <c r="P13">
-        <v>72.28446428750001</v>
+        <v>72.07805195</v>
       </c>
       <c r="Q13">
-        <v>93.58446428750001</v>
+        <v>93.37805195</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1714189874146638</v>
+        <v>0.1725533668889986</v>
       </c>
       <c r="T13">
-        <v>0.8758711735466828</v>
+        <v>0.8837805692668791</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>32.83586317957992</v>
+        <v>30.09954124794826</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2384,22 +2384,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1565248628623188</v>
+        <v>0.1561987519255868</v>
       </c>
       <c r="C14">
-        <v>579.5635639944106</v>
+        <v>576.1118310896353</v>
       </c>
       <c r="D14">
-        <v>624.0035639944106</v>
+        <v>625.8468310896353</v>
       </c>
       <c r="E14">
-        <v>-293.36</v>
+        <v>-288.0649999999999</v>
       </c>
       <c r="F14">
-        <v>63.54</v>
+        <v>68.83500000000001</v>
       </c>
       <c r="G14">
         <v>19.1</v>
@@ -2420,28 +2420,28 @@
         <v>96.2</v>
       </c>
       <c r="M14">
-        <v>3.196062</v>
+        <v>3.4624005</v>
       </c>
       <c r="N14">
-        <v>93.00393800000001</v>
+        <v>92.7375995</v>
       </c>
       <c r="O14">
-        <v>20.92588605</v>
+        <v>20.8659598875</v>
       </c>
       <c r="P14">
-        <v>72.07805195</v>
+        <v>71.8716396125</v>
       </c>
       <c r="Q14">
-        <v>93.37805195</v>
+        <v>93.1716396125</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1725533668889986</v>
+        <v>0.1737138240523986</v>
       </c>
       <c r="T14">
-        <v>0.8837805692668791</v>
+        <v>0.8918717901760453</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>30.09954124794826</v>
+        <v>27.78419192118301</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2466,22 +2466,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1561987519255868</v>
+        <v>0.1558726409888548</v>
       </c>
       <c r="C15">
-        <v>576.1118310896353</v>
+        <v>572.6710202369463</v>
       </c>
       <c r="D15">
-        <v>625.8468310896353</v>
+        <v>627.7010202369463</v>
       </c>
       <c r="E15">
-        <v>-288.0649999999999</v>
+        <v>-282.77</v>
       </c>
       <c r="F15">
-        <v>68.83500000000001</v>
+        <v>74.13000000000001</v>
       </c>
       <c r="G15">
         <v>19.1</v>
@@ -2502,28 +2502,28 @@
         <v>96.2</v>
       </c>
       <c r="M15">
-        <v>3.4624005</v>
+        <v>3.728739</v>
       </c>
       <c r="N15">
-        <v>92.7375995</v>
+        <v>92.471261</v>
       </c>
       <c r="O15">
-        <v>20.8659598875</v>
+        <v>20.806033725</v>
       </c>
       <c r="P15">
-        <v>71.8716396125</v>
+        <v>71.66522727500001</v>
       </c>
       <c r="Q15">
-        <v>93.1716396125</v>
+        <v>92.965227275</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1737138240523986</v>
+        <v>0.1749012685916916</v>
       </c>
       <c r="T15">
-        <v>0.8918717901760453</v>
+        <v>0.9001511790133316</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.78419192118301</v>
+        <v>25.79960678395565</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2548,22 +2548,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1558726409888548</v>
+        <v>0.1555465300521228</v>
       </c>
       <c r="C16">
-        <v>572.6710202369463</v>
+        <v>569.2412288007147</v>
       </c>
       <c r="D16">
-        <v>627.7010202369463</v>
+        <v>629.5662288007147</v>
       </c>
       <c r="E16">
-        <v>-282.77</v>
+        <v>-277.475</v>
       </c>
       <c r="F16">
-        <v>74.13000000000001</v>
+        <v>79.42500000000001</v>
       </c>
       <c r="G16">
         <v>19.1</v>
@@ -2584,28 +2584,28 @@
         <v>96.2</v>
       </c>
       <c r="M16">
-        <v>3.728739</v>
+        <v>3.9950775</v>
       </c>
       <c r="N16">
-        <v>92.471261</v>
+        <v>92.20492250000001</v>
       </c>
       <c r="O16">
-        <v>20.806033725</v>
+        <v>20.7461075625</v>
       </c>
       <c r="P16">
-        <v>71.66522727500001</v>
+        <v>71.45881493750001</v>
       </c>
       <c r="Q16">
-        <v>92.965227275</v>
+        <v>92.75881493750001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1749012685916916</v>
+        <v>0.1761166530024975</v>
       </c>
       <c r="T16">
-        <v>0.9001511790133316</v>
+        <v>0.9086253769997307</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.79960678395565</v>
+        <v>24.0796329983586</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2630,22 +2630,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1555465300521228</v>
+        <v>0.1552204191153908</v>
       </c>
       <c r="C17">
-        <v>569.2412288007148</v>
+        <v>565.8225553060309</v>
       </c>
       <c r="D17">
-        <v>629.5662288007147</v>
+        <v>631.442555306031</v>
       </c>
       <c r="E17">
-        <v>-277.475</v>
+        <v>-272.1799999999999</v>
       </c>
       <c r="F17">
-        <v>79.425</v>
+        <v>84.72</v>
       </c>
       <c r="G17">
         <v>19.1</v>
@@ -2666,28 +2666,28 @@
         <v>96.2</v>
       </c>
       <c r="M17">
-        <v>3.9950775</v>
+        <v>4.261416</v>
       </c>
       <c r="N17">
-        <v>92.20492250000001</v>
+        <v>91.93858400000001</v>
       </c>
       <c r="O17">
-        <v>20.7461075625</v>
+        <v>20.6861814</v>
       </c>
       <c r="P17">
-        <v>71.45881493750001</v>
+        <v>71.25240260000001</v>
       </c>
       <c r="Q17">
-        <v>92.75881493750001</v>
+        <v>92.55240260000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1761166530024975</v>
+        <v>0.1773609751373701</v>
       </c>
       <c r="T17">
-        <v>0.9086253769997307</v>
+        <v>0.9173013416048534</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>24.07963299835861</v>
+        <v>22.5746559359612</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2712,22 +2712,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1552204191153908</v>
+        <v>0.1548943081786589</v>
       </c>
       <c r="C18">
-        <v>565.8225553060309</v>
+        <v>562.4150994560525</v>
       </c>
       <c r="D18">
-        <v>631.442555306031</v>
+        <v>633.3300994560525</v>
       </c>
       <c r="E18">
-        <v>-272.1799999999999</v>
+        <v>-266.885</v>
       </c>
       <c r="F18">
-        <v>84.72</v>
+        <v>90.015</v>
       </c>
       <c r="G18">
         <v>19.1</v>
@@ -2748,28 +2748,28 @@
         <v>96.2</v>
       </c>
       <c r="M18">
-        <v>4.261416</v>
+        <v>4.527754499999999</v>
       </c>
       <c r="N18">
-        <v>91.93858400000001</v>
+        <v>91.6722455</v>
       </c>
       <c r="O18">
-        <v>20.6861814</v>
+        <v>20.6262552375</v>
       </c>
       <c r="P18">
-        <v>71.25240260000001</v>
+        <v>71.0459902625</v>
       </c>
       <c r="Q18">
-        <v>92.55240260000001</v>
+        <v>92.3459902625</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1773609751373701</v>
+        <v>0.1786352809381432</v>
       </c>
       <c r="T18">
-        <v>0.9173013416048534</v>
+        <v>0.9261863655980515</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.5746559359612</v>
+        <v>21.24673499855171</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2794,22 +2794,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1548943081786589</v>
+        <v>0.1545681972419269</v>
       </c>
       <c r="C19">
-        <v>562.4150994560525</v>
+        <v>559.0189621496648</v>
       </c>
       <c r="D19">
-        <v>633.3300994560525</v>
+        <v>635.2289621496649</v>
       </c>
       <c r="E19">
-        <v>-266.885</v>
+        <v>-261.59</v>
       </c>
       <c r="F19">
-        <v>90.015</v>
+        <v>95.31000000000002</v>
       </c>
       <c r="G19">
         <v>19.1</v>
@@ -2830,28 +2830,28 @@
         <v>96.2</v>
       </c>
       <c r="M19">
-        <v>4.527754499999999</v>
+        <v>4.794093</v>
       </c>
       <c r="N19">
-        <v>91.6722455</v>
+        <v>91.405907</v>
       </c>
       <c r="O19">
-        <v>20.6262552375</v>
+        <v>20.566329075</v>
       </c>
       <c r="P19">
-        <v>71.0459902625</v>
+        <v>70.839577925</v>
       </c>
       <c r="Q19">
-        <v>92.3459902625</v>
+        <v>92.139577925</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1786352809381432</v>
+        <v>0.1799406673682035</v>
       </c>
       <c r="T19">
-        <v>0.9261863655980515</v>
+        <v>0.9352880974935227</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>21.24673499855171</v>
+        <v>20.0663608319655</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2876,22 +2876,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1545681972419269</v>
+        <v>0.1542420863051949</v>
       </c>
       <c r="C20">
-        <v>559.0189621496647</v>
+        <v>555.6342454994605</v>
       </c>
       <c r="D20">
-        <v>635.2289621496648</v>
+        <v>637.1392454994605</v>
       </c>
       <c r="E20">
-        <v>-261.59</v>
+        <v>-256.295</v>
       </c>
       <c r="F20">
-        <v>95.31</v>
+        <v>100.605</v>
       </c>
       <c r="G20">
         <v>19.1</v>
@@ -2912,28 +2912,28 @@
         <v>96.2</v>
       </c>
       <c r="M20">
-        <v>4.794093</v>
+        <v>5.0604315</v>
       </c>
       <c r="N20">
-        <v>91.405907</v>
+        <v>91.1395685</v>
       </c>
       <c r="O20">
-        <v>20.566329075</v>
+        <v>20.5064029125</v>
       </c>
       <c r="P20">
-        <v>70.839577925</v>
+        <v>70.6331655875</v>
       </c>
       <c r="Q20">
-        <v>92.139577925</v>
+        <v>91.9331655875</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1799406673682035</v>
+        <v>0.181278285561969</v>
       </c>
       <c r="T20">
-        <v>0.9352880974935227</v>
+        <v>0.9446145635098696</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>20.0663608319655</v>
+        <v>19.01023657765153</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2958,22 +2958,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1542420863051949</v>
+        <v>0.153915975368463</v>
       </c>
       <c r="C21">
-        <v>555.6342454994605</v>
+        <v>552.2610528500431</v>
       </c>
       <c r="D21">
-        <v>637.1392454994605</v>
+        <v>639.0610528500431</v>
       </c>
       <c r="E21">
-        <v>-256.295</v>
+        <v>-251</v>
       </c>
       <c r="F21">
-        <v>100.605</v>
+        <v>105.9</v>
       </c>
       <c r="G21">
         <v>19.1</v>
@@ -2994,28 +2994,28 @@
         <v>96.2</v>
       </c>
       <c r="M21">
-        <v>5.0604315</v>
+        <v>5.32677</v>
       </c>
       <c r="N21">
-        <v>91.1395685</v>
+        <v>90.87323000000001</v>
       </c>
       <c r="O21">
-        <v>20.5064029125</v>
+        <v>20.44647675</v>
       </c>
       <c r="P21">
-        <v>70.6331655875</v>
+        <v>70.42675325</v>
       </c>
       <c r="Q21">
-        <v>91.9331655875</v>
+        <v>91.72675325</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.181278285561969</v>
+        <v>0.1826493442105787</v>
       </c>
       <c r="T21">
-        <v>0.9446145635098696</v>
+        <v>0.9541741911766255</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>19.01023657765153</v>
+        <v>18.05972474876896</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3040,22 +3040,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.153915975368463</v>
+        <v>0.1535898644317309</v>
       </c>
       <c r="C22">
-        <v>552.2610528500431</v>
+        <v>548.8994887966655</v>
       </c>
       <c r="D22">
-        <v>639.0610528500431</v>
+        <v>640.9944887966656</v>
       </c>
       <c r="E22">
-        <v>-251</v>
+        <v>-245.705</v>
       </c>
       <c r="F22">
-        <v>105.9</v>
+        <v>111.195</v>
       </c>
       <c r="G22">
         <v>19.1</v>
@@ -3076,28 +3076,28 @@
         <v>96.2</v>
       </c>
       <c r="M22">
-        <v>5.32677</v>
+        <v>5.5931085</v>
       </c>
       <c r="N22">
-        <v>90.87323000000001</v>
+        <v>90.6068915</v>
       </c>
       <c r="O22">
-        <v>20.44647675</v>
+        <v>20.3865505875</v>
       </c>
       <c r="P22">
-        <v>70.42675325</v>
+        <v>70.22034091250001</v>
       </c>
       <c r="Q22">
-        <v>91.72675325</v>
+        <v>91.5203409125</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1826493442105787</v>
+        <v>0.1840551132047227</v>
       </c>
       <c r="T22">
-        <v>0.9541741911766255</v>
+        <v>0.9639758347336786</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>18.05972474876896</v>
+        <v>17.19973785597043</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3122,22 +3122,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1535898644317309</v>
+        <v>0.153263753494999</v>
       </c>
       <c r="C23">
-        <v>548.8994887966655</v>
+        <v>545.5496592042043</v>
       </c>
       <c r="D23">
-        <v>640.9944887966656</v>
+        <v>642.9396592042043</v>
       </c>
       <c r="E23">
-        <v>-245.705</v>
+        <v>-240.41</v>
       </c>
       <c r="F23">
-        <v>111.195</v>
+        <v>116.49</v>
       </c>
       <c r="G23">
         <v>19.1</v>
@@ -3158,28 +3158,28 @@
         <v>96.2</v>
       </c>
       <c r="M23">
-        <v>5.5931085</v>
+        <v>5.859446999999999</v>
       </c>
       <c r="N23">
-        <v>90.6068915</v>
+        <v>90.340553</v>
       </c>
       <c r="O23">
-        <v>20.3865505875</v>
+        <v>20.326624425</v>
       </c>
       <c r="P23">
-        <v>70.22034091250001</v>
+        <v>70.01392857499999</v>
       </c>
       <c r="Q23">
-        <v>91.5203409125</v>
+        <v>91.31392857499999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1840551132047227</v>
+        <v>0.185496927557691</v>
       </c>
       <c r="T23">
-        <v>0.9639758347336786</v>
+        <v>0.9740288024845026</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>17.19973785597043</v>
+        <v>16.41793158978996</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3204,22 +3204,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.153263753494999</v>
+        <v>0.152937642558267</v>
       </c>
       <c r="C24">
-        <v>545.5496592042043</v>
+        <v>542.2116712264842</v>
       </c>
       <c r="D24">
-        <v>642.9396592042043</v>
+        <v>644.8966712264842</v>
       </c>
       <c r="E24">
-        <v>-240.41</v>
+        <v>-235.115</v>
       </c>
       <c r="F24">
-        <v>116.49</v>
+        <v>121.785</v>
       </c>
       <c r="G24">
         <v>19.1</v>
@@ -3240,28 +3240,28 @@
         <v>96.2</v>
       </c>
       <c r="M24">
-        <v>5.859446999999999</v>
+        <v>6.1257855</v>
       </c>
       <c r="N24">
-        <v>90.340553</v>
+        <v>90.0742145</v>
       </c>
       <c r="O24">
-        <v>20.326624425</v>
+        <v>20.2666982625</v>
       </c>
       <c r="P24">
-        <v>70.01392857499999</v>
+        <v>69.8075162375</v>
       </c>
       <c r="Q24">
-        <v>91.31392857499999</v>
+        <v>91.10751623749999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.185496927557691</v>
+        <v>0.186976191634113</v>
       </c>
       <c r="T24">
-        <v>0.9740288024845026</v>
+        <v>0.9843428862808022</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.41793158978996</v>
+        <v>15.70410847719039</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3286,22 +3286,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.152937642558267</v>
+        <v>0.152611531621535</v>
       </c>
       <c r="C25">
-        <v>542.2116712264842</v>
+        <v>538.8856333259525</v>
       </c>
       <c r="D25">
-        <v>644.8966712264842</v>
+        <v>646.8656333259526</v>
       </c>
       <c r="E25">
-        <v>-235.115</v>
+        <v>-229.82</v>
       </c>
       <c r="F25">
-        <v>121.785</v>
+        <v>127.08</v>
       </c>
       <c r="G25">
         <v>19.1</v>
@@ -3322,28 +3322,28 @@
         <v>96.2</v>
       </c>
       <c r="M25">
-        <v>6.1257855</v>
+        <v>6.392124</v>
       </c>
       <c r="N25">
-        <v>90.0742145</v>
+        <v>89.80787600000001</v>
       </c>
       <c r="O25">
-        <v>20.2666982625</v>
+        <v>20.2067721</v>
       </c>
       <c r="P25">
-        <v>69.8075162375</v>
+        <v>69.6011039</v>
       </c>
       <c r="Q25">
-        <v>91.10751623749999</v>
+        <v>90.9011039</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.186976191634113</v>
+        <v>0.1884943837125461</v>
       </c>
       <c r="T25">
-        <v>0.9843428862808022</v>
+        <v>0.9949283933348996</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.70410847719039</v>
+        <v>15.04977062397413</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3368,22 +3368,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.152611531621535</v>
+        <v>0.152285420684803</v>
       </c>
       <c r="C26">
-        <v>538.8856333259525</v>
+        <v>535.5716552937212</v>
       </c>
       <c r="D26">
-        <v>646.8656333259526</v>
+        <v>648.8466552937211</v>
       </c>
       <c r="E26">
-        <v>-229.82</v>
+        <v>-224.525</v>
       </c>
       <c r="F26">
-        <v>127.08</v>
+        <v>132.375</v>
       </c>
       <c r="G26">
         <v>19.1</v>
@@ -3404,28 +3404,28 @@
         <v>96.2</v>
       </c>
       <c r="M26">
-        <v>6.392124</v>
+        <v>6.6584625</v>
       </c>
       <c r="N26">
-        <v>89.80787600000001</v>
+        <v>89.5415375</v>
       </c>
       <c r="O26">
-        <v>20.2067721</v>
+        <v>20.1468459375</v>
       </c>
       <c r="P26">
-        <v>69.6011039</v>
+        <v>69.3946915625</v>
       </c>
       <c r="Q26">
-        <v>90.9011039</v>
+        <v>90.6946915625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1884943837125461</v>
+        <v>0.1900530609130707</v>
       </c>
       <c r="T26">
-        <v>0.9949283933348996</v>
+        <v>1.005796180577106</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.04977062397413</v>
+        <v>14.44777979901516</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3450,22 +3450,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.152285420684803</v>
+        <v>0.1519593097480711</v>
       </c>
       <c r="C27">
-        <v>535.5716552937212</v>
+        <v>532.2698482699695</v>
       </c>
       <c r="D27">
-        <v>648.8466552937211</v>
+        <v>650.8398482699696</v>
       </c>
       <c r="E27">
-        <v>-224.525</v>
+        <v>-219.23</v>
       </c>
       <c r="F27">
-        <v>132.375</v>
+        <v>137.67</v>
       </c>
       <c r="G27">
         <v>19.1</v>
@@ -3486,28 +3486,28 @@
         <v>96.2</v>
       </c>
       <c r="M27">
-        <v>6.6584625</v>
+        <v>6.924801</v>
       </c>
       <c r="N27">
-        <v>89.5415375</v>
+        <v>89.275199</v>
       </c>
       <c r="O27">
-        <v>20.1468459375</v>
+        <v>20.086919775</v>
       </c>
       <c r="P27">
-        <v>69.3946915625</v>
+        <v>69.188279225</v>
       </c>
       <c r="Q27">
-        <v>90.6946915625</v>
+        <v>90.488279225</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1900530609130707</v>
+        <v>0.1916538645244204</v>
       </c>
       <c r="T27">
-        <v>1.005796180577106</v>
+        <v>1.016957691798832</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.44777979901516</v>
+        <v>13.8920959605915</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3532,22 +3532,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1519593097480711</v>
+        <v>0.1516331988113391</v>
       </c>
       <c r="C28">
-        <v>532.2698482699695</v>
+        <v>528.9803247647335</v>
       </c>
       <c r="D28">
-        <v>650.8398482699696</v>
+        <v>652.8453247647335</v>
       </c>
       <c r="E28">
-        <v>-219.23</v>
+        <v>-213.935</v>
       </c>
       <c r="F28">
-        <v>137.67</v>
+        <v>142.965</v>
       </c>
       <c r="G28">
         <v>19.1</v>
@@ -3568,28 +3568,28 @@
         <v>96.2</v>
       </c>
       <c r="M28">
-        <v>6.924801</v>
+        <v>7.1911395</v>
       </c>
       <c r="N28">
-        <v>89.275199</v>
+        <v>89.0088605</v>
       </c>
       <c r="O28">
-        <v>20.086919775</v>
+        <v>20.0269936125</v>
       </c>
       <c r="P28">
-        <v>69.188279225</v>
+        <v>68.98186688749999</v>
       </c>
       <c r="Q28">
-        <v>90.488279225</v>
+        <v>90.28186688749999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1916538645244204</v>
+        <v>0.1932985257689576</v>
       </c>
       <c r="T28">
-        <v>1.016957691798832</v>
+        <v>1.02842499784855</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.8920959605915</v>
+        <v>13.377573887977</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3614,22 +3614,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1516331988113391</v>
+        <v>0.1513070878746071</v>
       </c>
       <c r="C29">
-        <v>528.9803247647335</v>
+        <v>525.7031986790731</v>
       </c>
       <c r="D29">
-        <v>652.8453247647335</v>
+        <v>654.8631986790731</v>
       </c>
       <c r="E29">
-        <v>-213.935</v>
+        <v>-208.64</v>
       </c>
       <c r="F29">
-        <v>142.965</v>
+        <v>148.26</v>
       </c>
       <c r="G29">
         <v>19.1</v>
@@ -3650,28 +3650,28 @@
         <v>96.2</v>
       </c>
       <c r="M29">
-        <v>7.1911395</v>
+        <v>7.457478000000001</v>
       </c>
       <c r="N29">
-        <v>89.0088605</v>
+        <v>88.74252200000001</v>
       </c>
       <c r="O29">
-        <v>20.0269936125</v>
+        <v>19.96706745</v>
       </c>
       <c r="P29">
-        <v>68.98186688749999</v>
+        <v>68.77545455000001</v>
       </c>
       <c r="Q29">
-        <v>90.28186688749999</v>
+        <v>90.07545455</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1932985257689576</v>
+        <v>0.1949888720480654</v>
       </c>
       <c r="T29">
-        <v>1.02842499784855</v>
+        <v>1.040210840177426</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>13.377573887977</v>
+        <v>12.89980339197782</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3696,22 +3696,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1513070878746071</v>
+        <v>0.1513181019378751</v>
       </c>
       <c r="C30">
-        <v>525.7031986790731</v>
+        <v>520.3398435383945</v>
       </c>
       <c r="D30">
-        <v>654.8631986790731</v>
+        <v>654.7948435383944</v>
       </c>
       <c r="E30">
-        <v>-208.64</v>
+        <v>-203.345</v>
       </c>
       <c r="F30">
-        <v>148.26</v>
+        <v>153.555</v>
       </c>
       <c r="G30">
         <v>19.1</v>
@@ -3732,45 +3732,45 @@
         <v>96.2</v>
       </c>
       <c r="M30">
-        <v>7.457478000000001</v>
+        <v>7.954149</v>
       </c>
       <c r="N30">
-        <v>88.74252200000001</v>
+        <v>88.245851</v>
       </c>
       <c r="O30">
-        <v>19.96706745</v>
+        <v>19.855316475</v>
       </c>
       <c r="P30">
-        <v>68.77545455000001</v>
+        <v>68.39053452499999</v>
       </c>
       <c r="Q30">
-        <v>90.07545455</v>
+        <v>89.69053452499999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1949888720480654</v>
+        <v>0.1967268337153171</v>
       </c>
       <c r="T30">
-        <v>1.040210840177426</v>
+        <v>1.052328678064863</v>
       </c>
       <c r="U30">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V30">
         <v>0.225</v>
       </c>
       <c r="W30">
-        <v>0.0389825</v>
+        <v>0.040145</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y30">
-        <v>12.89980339197782</v>
+        <v>12.09431706647688</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3778,22 +3778,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1513181019378751</v>
+        <v>0.1510036160011431</v>
       </c>
       <c r="C31">
-        <v>520.3398435383945</v>
+        <v>517.0022265406591</v>
       </c>
       <c r="D31">
-        <v>654.7948435383944</v>
+        <v>656.7522265406591</v>
       </c>
       <c r="E31">
-        <v>-203.345</v>
+        <v>-198.05</v>
       </c>
       <c r="F31">
-        <v>153.555</v>
+        <v>158.85</v>
       </c>
       <c r="G31">
         <v>19.1</v>
@@ -3814,28 +3814,28 @@
         <v>96.2</v>
       </c>
       <c r="M31">
-        <v>7.954148999999998</v>
+        <v>8.228429999999999</v>
       </c>
       <c r="N31">
-        <v>88.245851</v>
+        <v>87.97157</v>
       </c>
       <c r="O31">
-        <v>19.855316475</v>
+        <v>19.79360325</v>
       </c>
       <c r="P31">
-        <v>68.39053452499999</v>
+        <v>68.17796675</v>
       </c>
       <c r="Q31">
-        <v>89.69053452499999</v>
+        <v>89.47796674999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.196726833715317</v>
+        <v>0.1985144514302045</v>
       </c>
       <c r="T31">
-        <v>1.052328678064863</v>
+        <v>1.064792739891941</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>12.09431706647688</v>
+        <v>11.69117316426098</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3860,22 +3860,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1510036160011431</v>
+        <v>0.1506891300644111</v>
       </c>
       <c r="C32">
-        <v>517.0022265406591</v>
+        <v>513.6763470685693</v>
       </c>
       <c r="D32">
-        <v>656.7522265406591</v>
+        <v>658.7213470685692</v>
       </c>
       <c r="E32">
-        <v>-198.05</v>
+        <v>-192.755</v>
       </c>
       <c r="F32">
-        <v>158.85</v>
+        <v>164.145</v>
       </c>
       <c r="G32">
         <v>19.1</v>
@@ -3896,28 +3896,28 @@
         <v>96.2</v>
       </c>
       <c r="M32">
-        <v>8.228429999999999</v>
+        <v>8.502711</v>
       </c>
       <c r="N32">
-        <v>87.97157</v>
+        <v>87.697289</v>
       </c>
       <c r="O32">
-        <v>19.79360325</v>
+        <v>19.731890025</v>
       </c>
       <c r="P32">
-        <v>68.17796675</v>
+        <v>67.965398975</v>
       </c>
       <c r="Q32">
-        <v>89.47796674999999</v>
+        <v>89.265398975</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1985144514302045</v>
+        <v>0.2003538841513205</v>
       </c>
       <c r="T32">
-        <v>1.064792739891941</v>
+        <v>1.077618078873427</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.69117316426098</v>
+        <v>11.31403854605902</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3942,22 +3942,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1506891300644111</v>
+        <v>0.1503746441276792</v>
       </c>
       <c r="C33">
-        <v>513.6763470685693</v>
+        <v>510.3623110164387</v>
       </c>
       <c r="D33">
-        <v>658.7213470685692</v>
+        <v>660.7023110164387</v>
       </c>
       <c r="E33">
-        <v>-192.755</v>
+        <v>-187.46</v>
       </c>
       <c r="F33">
-        <v>164.145</v>
+        <v>169.44</v>
       </c>
       <c r="G33">
         <v>19.1</v>
@@ -3978,28 +3978,28 @@
         <v>96.2</v>
       </c>
       <c r="M33">
-        <v>8.502711</v>
+        <v>8.776992</v>
       </c>
       <c r="N33">
-        <v>87.697289</v>
+        <v>87.42300800000001</v>
       </c>
       <c r="O33">
-        <v>19.731890025</v>
+        <v>19.6701768</v>
       </c>
       <c r="P33">
-        <v>67.965398975</v>
+        <v>67.7528312</v>
       </c>
       <c r="Q33">
-        <v>89.265398975</v>
+        <v>89.0528312</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2003538841513205</v>
+        <v>0.2022474178348223</v>
       </c>
       <c r="T33">
-        <v>1.077618078873427</v>
+        <v>1.090820633707309</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.31403854605902</v>
+        <v>10.96047484149467</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4024,22 +4024,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1503746441276792</v>
+        <v>0.1500601581909472</v>
       </c>
       <c r="C34">
-        <v>510.3623110164387</v>
+        <v>507.0602255562424</v>
       </c>
       <c r="D34">
-        <v>660.7023110164387</v>
+        <v>662.6952255562423</v>
       </c>
       <c r="E34">
-        <v>-187.46</v>
+        <v>-182.165</v>
       </c>
       <c r="F34">
-        <v>169.44</v>
+        <v>174.735</v>
       </c>
       <c r="G34">
         <v>19.1</v>
@@ -4060,28 +4060,28 @@
         <v>96.2</v>
       </c>
       <c r="M34">
-        <v>8.776992</v>
+        <v>9.051273</v>
       </c>
       <c r="N34">
-        <v>87.42300800000001</v>
+        <v>87.14872700000001</v>
       </c>
       <c r="O34">
-        <v>19.6701768</v>
+        <v>19.608463575</v>
       </c>
       <c r="P34">
-        <v>67.7528312</v>
+        <v>67.54026342500001</v>
       </c>
       <c r="Q34">
-        <v>89.0528312</v>
+        <v>88.840263425</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2022474178348223</v>
+        <v>0.2041974749118615</v>
       </c>
       <c r="T34">
-        <v>1.090820633707309</v>
+        <v>1.104417294655636</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.96047484149467</v>
+        <v>10.62833924023726</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4106,22 +4106,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1500601581909472</v>
+        <v>0.1497456722542152</v>
       </c>
       <c r="C35">
-        <v>507.0602255562424</v>
+        <v>503.7701991569438</v>
       </c>
       <c r="D35">
-        <v>662.6952255562423</v>
+        <v>664.7001991569438</v>
       </c>
       <c r="E35">
-        <v>-182.165</v>
+        <v>-176.87</v>
       </c>
       <c r="F35">
-        <v>174.735</v>
+        <v>180.03</v>
       </c>
       <c r="G35">
         <v>19.1</v>
@@ -4142,28 +4142,28 @@
         <v>96.2</v>
       </c>
       <c r="M35">
-        <v>9.051273</v>
+        <v>9.325554</v>
       </c>
       <c r="N35">
-        <v>87.14872700000001</v>
+        <v>86.87444600000001</v>
       </c>
       <c r="O35">
-        <v>19.608463575</v>
+        <v>19.54675035</v>
       </c>
       <c r="P35">
-        <v>67.54026342500001</v>
+        <v>67.32769565000001</v>
       </c>
       <c r="Q35">
-        <v>88.840263425</v>
+        <v>88.62769565000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2041974749118615</v>
+        <v>0.2062066246275988</v>
       </c>
       <c r="T35">
-        <v>1.104417294655636</v>
+        <v>1.1184259756327</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.62833924023726</v>
+        <v>10.3157410272891</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4188,22 +4188,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1497456722542152</v>
+        <v>0.1494311863174832</v>
       </c>
       <c r="C36">
-        <v>503.7701991569438</v>
+        <v>500.4923416041739</v>
       </c>
       <c r="D36">
-        <v>664.7001991569438</v>
+        <v>666.717341604174</v>
       </c>
       <c r="E36">
-        <v>-176.87</v>
+        <v>-171.575</v>
       </c>
       <c r="F36">
-        <v>180.03</v>
+        <v>185.325</v>
       </c>
       <c r="G36">
         <v>19.1</v>
@@ -4224,28 +4224,28 @@
         <v>96.2</v>
       </c>
       <c r="M36">
-        <v>9.325554</v>
+        <v>9.599835000000001</v>
       </c>
       <c r="N36">
-        <v>86.87444600000001</v>
+        <v>86.600165</v>
       </c>
       <c r="O36">
-        <v>19.54675035</v>
+        <v>19.485037125</v>
       </c>
       <c r="P36">
-        <v>67.32769565000001</v>
+        <v>67.115127875</v>
       </c>
       <c r="Q36">
-        <v>88.62769565000001</v>
+        <v>88.415127875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2062066246275988</v>
+        <v>0.2082775943345896</v>
       </c>
       <c r="T36">
-        <v>1.1184259756327</v>
+        <v>1.13286569294752</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.3157410272891</v>
+        <v>10.02100556936656</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4270,22 +4270,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1494311863174832</v>
+        <v>0.1495910003807512</v>
       </c>
       <c r="C37">
-        <v>500.4923416041739</v>
+        <v>494.170751562435</v>
       </c>
       <c r="D37">
-        <v>666.717341604174</v>
+        <v>665.690751562435</v>
       </c>
       <c r="E37">
-        <v>-171.575</v>
+        <v>-166.2799999999999</v>
       </c>
       <c r="F37">
-        <v>185.325</v>
+        <v>190.62</v>
       </c>
       <c r="G37">
         <v>19.1</v>
@@ -4306,45 +4306,45 @@
         <v>96.2</v>
       </c>
       <c r="M37">
-        <v>9.599835000000001</v>
+        <v>10.19817</v>
       </c>
       <c r="N37">
-        <v>86.600165</v>
+        <v>86.00183</v>
       </c>
       <c r="O37">
-        <v>19.485037125</v>
+        <v>19.35041175</v>
       </c>
       <c r="P37">
-        <v>67.115127875</v>
+        <v>66.65141825000001</v>
       </c>
       <c r="Q37">
-        <v>88.415127875</v>
+        <v>87.95141825</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2082775943345896</v>
+        <v>0.2104132818449238</v>
       </c>
       <c r="T37">
-        <v>1.13286569294752</v>
+        <v>1.147756651428428</v>
       </c>
       <c r="U37">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V37">
         <v>0.225</v>
       </c>
       <c r="W37">
-        <v>0.040145</v>
+        <v>0.0414625</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>10.02100556936656</v>
+        <v>9.433064951849204</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4352,22 +4352,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1495910003807513</v>
+        <v>0.1492896894440193</v>
       </c>
       <c r="C38">
-        <v>494.1707515624349</v>
+        <v>490.8139147263662</v>
       </c>
       <c r="D38">
-        <v>665.6907515624349</v>
+        <v>667.6289147263661</v>
       </c>
       <c r="E38">
-        <v>-166.28</v>
+        <v>-160.985</v>
       </c>
       <c r="F38">
-        <v>190.62</v>
+        <v>195.915</v>
       </c>
       <c r="G38">
         <v>19.1</v>
@@ -4388,28 +4388,28 @@
         <v>96.2</v>
       </c>
       <c r="M38">
-        <v>10.19817</v>
+        <v>10.4814525</v>
       </c>
       <c r="N38">
-        <v>86.00183</v>
+        <v>85.7185475</v>
       </c>
       <c r="O38">
-        <v>19.35041175</v>
+        <v>19.2866731875</v>
       </c>
       <c r="P38">
-        <v>66.65141825000001</v>
+        <v>66.4318743125</v>
       </c>
       <c r="Q38">
-        <v>87.95141825</v>
+        <v>87.7318743125</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2104132818449238</v>
+        <v>0.2126167689587607</v>
       </c>
       <c r="T38">
-        <v>1.147756651428428</v>
+        <v>1.163120338749999</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.433064951849206</v>
+        <v>9.178117250447874</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4434,22 +4434,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1492896894440193</v>
+        <v>0.1489883785072873</v>
       </c>
       <c r="C39">
-        <v>490.8139147263662</v>
+        <v>487.4683967959129</v>
       </c>
       <c r="D39">
-        <v>667.6289147263661</v>
+        <v>669.5783967959129</v>
       </c>
       <c r="E39">
-        <v>-160.985</v>
+        <v>-155.69</v>
       </c>
       <c r="F39">
-        <v>195.915</v>
+        <v>201.21</v>
       </c>
       <c r="G39">
         <v>19.1</v>
@@ -4470,28 +4470,28 @@
         <v>96.2</v>
       </c>
       <c r="M39">
-        <v>10.4814525</v>
+        <v>10.764735</v>
       </c>
       <c r="N39">
-        <v>85.7185475</v>
+        <v>85.435265</v>
       </c>
       <c r="O39">
-        <v>19.2866731875</v>
+        <v>19.222934625</v>
       </c>
       <c r="P39">
-        <v>66.4318743125</v>
+        <v>66.21233037499999</v>
       </c>
       <c r="Q39">
-        <v>87.7318743125</v>
+        <v>87.51233037499999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2126167689587607</v>
+        <v>0.2148913363020763</v>
       </c>
       <c r="T39">
-        <v>1.163120338749999</v>
+        <v>1.178979628888396</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.178117250447874</v>
+        <v>8.936587849120299</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4516,22 +4516,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1489883785072873</v>
+        <v>0.1486870675705553</v>
       </c>
       <c r="C40">
-        <v>487.4683967959129</v>
+        <v>484.1342972153532</v>
       </c>
       <c r="D40">
-        <v>669.5783967959129</v>
+        <v>671.5392972153531</v>
       </c>
       <c r="E40">
-        <v>-155.69</v>
+        <v>-150.395</v>
       </c>
       <c r="F40">
-        <v>201.21</v>
+        <v>206.505</v>
       </c>
       <c r="G40">
         <v>19.1</v>
@@ -4552,28 +4552,28 @@
         <v>96.2</v>
       </c>
       <c r="M40">
-        <v>10.764735</v>
+        <v>11.0480175</v>
       </c>
       <c r="N40">
-        <v>85.435265</v>
+        <v>85.1519825</v>
       </c>
       <c r="O40">
-        <v>19.222934625</v>
+        <v>19.1591960625</v>
       </c>
       <c r="P40">
-        <v>66.21233037499999</v>
+        <v>65.9927864375</v>
       </c>
       <c r="Q40">
-        <v>87.51233037499999</v>
+        <v>87.2927864375</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2148913363020763</v>
+        <v>0.2172404796238612</v>
       </c>
       <c r="T40">
-        <v>1.178979628888396</v>
+        <v>1.195358895752641</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4590,7 +4590,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.936587849120299</v>
+        <v>8.707444570937728</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4598,22 +4598,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1486870675705553</v>
+        <v>0.1483857566338233</v>
       </c>
       <c r="C41">
-        <v>484.1342972153532</v>
+        <v>480.8117165973007</v>
       </c>
       <c r="D41">
-        <v>671.5392972153531</v>
+        <v>673.5117165973007</v>
       </c>
       <c r="E41">
-        <v>-150.395</v>
+        <v>-145.1</v>
       </c>
       <c r="F41">
-        <v>206.505</v>
+        <v>211.8</v>
       </c>
       <c r="G41">
         <v>19.1</v>
@@ -4634,28 +4634,28 @@
         <v>96.2</v>
       </c>
       <c r="M41">
-        <v>11.0480175</v>
+        <v>11.3313</v>
       </c>
       <c r="N41">
-        <v>85.1519825</v>
+        <v>84.8687</v>
       </c>
       <c r="O41">
-        <v>19.1591960625</v>
+        <v>19.0954575</v>
       </c>
       <c r="P41">
-        <v>65.9927864375</v>
+        <v>65.77324250000001</v>
       </c>
       <c r="Q41">
-        <v>87.2927864375</v>
+        <v>87.07324250000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2172404796238612</v>
+        <v>0.2196679277230389</v>
       </c>
       <c r="T41">
-        <v>1.195358895752641</v>
+        <v>1.212284138179028</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.707444570937728</v>
+        <v>8.489758456664283</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4680,22 +4680,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1483857566338233</v>
+        <v>0.1480844456970913</v>
       </c>
       <c r="C42">
-        <v>480.8117165973007</v>
+        <v>477.5007567399132</v>
       </c>
       <c r="D42">
-        <v>673.5117165973007</v>
+        <v>675.4957567399132</v>
       </c>
       <c r="E42">
-        <v>-145.1</v>
+        <v>-139.8049999999999</v>
       </c>
       <c r="F42">
-        <v>211.8</v>
+        <v>217.095</v>
       </c>
       <c r="G42">
         <v>19.1</v>
@@ -4716,28 +4716,28 @@
         <v>96.2</v>
       </c>
       <c r="M42">
-        <v>11.3313</v>
+        <v>11.6145825</v>
       </c>
       <c r="N42">
-        <v>84.8687</v>
+        <v>84.58541750000001</v>
       </c>
       <c r="O42">
-        <v>19.0954575</v>
+        <v>19.0317189375</v>
       </c>
       <c r="P42">
-        <v>65.77324250000001</v>
+        <v>65.5536985625</v>
       </c>
       <c r="Q42">
-        <v>87.07324250000001</v>
+        <v>86.8536985625</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2196679277230389</v>
+        <v>0.2221776621984599</v>
       </c>
       <c r="T42">
-        <v>1.212284138179028</v>
+        <v>1.229783117636819</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4754,7 +4754,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.489758456664283</v>
+        <v>8.282691177233447</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4762,22 +4762,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1480844456970913</v>
+        <v>0.1477831347603594</v>
       </c>
       <c r="C43">
-        <v>477.5007567399132</v>
+        <v>474.2015206444063</v>
       </c>
       <c r="D43">
-        <v>675.4957567399132</v>
+        <v>677.4915206444063</v>
       </c>
       <c r="E43">
-        <v>-139.8049999999999</v>
+        <v>-134.51</v>
       </c>
       <c r="F43">
-        <v>217.095</v>
+        <v>222.39</v>
       </c>
       <c r="G43">
         <v>19.1</v>
@@ -4798,28 +4798,28 @@
         <v>96.2</v>
       </c>
       <c r="M43">
-        <v>11.6145825</v>
+        <v>11.897865</v>
       </c>
       <c r="N43">
-        <v>84.58541750000001</v>
+        <v>84.30213500000001</v>
       </c>
       <c r="O43">
-        <v>19.0317189375</v>
+        <v>18.967980375</v>
       </c>
       <c r="P43">
-        <v>65.5536985625</v>
+        <v>65.334154625</v>
       </c>
       <c r="Q43">
-        <v>86.8536985625</v>
+        <v>86.63415462499999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2221776621984599</v>
+        <v>0.2247739392419989</v>
       </c>
       <c r="T43">
-        <v>1.229783117636819</v>
+        <v>1.24788551017936</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.282691177233447</v>
+        <v>8.085484244442174</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4844,22 +4844,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1477831347603594</v>
+        <v>0.1474818238236274</v>
       </c>
       <c r="C44">
-        <v>474.2015206444063</v>
+        <v>470.9141125328779</v>
       </c>
       <c r="D44">
-        <v>677.4915206444063</v>
+        <v>679.4991125328779</v>
       </c>
       <c r="E44">
-        <v>-134.51</v>
+        <v>-129.215</v>
       </c>
       <c r="F44">
-        <v>222.39</v>
+        <v>227.685</v>
       </c>
       <c r="G44">
         <v>19.1</v>
@@ -4880,28 +4880,28 @@
         <v>96.2</v>
       </c>
       <c r="M44">
-        <v>11.897865</v>
+        <v>12.1811475</v>
       </c>
       <c r="N44">
-        <v>84.30213500000001</v>
+        <v>84.01885250000001</v>
       </c>
       <c r="O44">
-        <v>18.967980375</v>
+        <v>18.9042418125</v>
       </c>
       <c r="P44">
-        <v>65.334154625</v>
+        <v>65.1146106875</v>
       </c>
       <c r="Q44">
-        <v>86.63415462499999</v>
+        <v>86.4146106875</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2247739392419989</v>
+        <v>0.2274613137256621</v>
       </c>
       <c r="T44">
-        <v>1.24788551017936</v>
+        <v>1.266623074390061</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.085484244442176</v>
+        <v>7.897449727129567</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4926,22 +4926,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1474818238236274</v>
+        <v>0.1471805128868954</v>
       </c>
       <c r="C45">
-        <v>470.9141125328779</v>
+        <v>467.6386378664521</v>
       </c>
       <c r="D45">
-        <v>679.4991125328779</v>
+        <v>681.5186378664521</v>
       </c>
       <c r="E45">
-        <v>-129.215</v>
+        <v>-123.92</v>
       </c>
       <c r="F45">
-        <v>227.685</v>
+        <v>232.98</v>
       </c>
       <c r="G45">
         <v>19.1</v>
@@ -4962,28 +4962,28 @@
         <v>96.2</v>
       </c>
       <c r="M45">
-        <v>12.1811475</v>
+        <v>12.46443</v>
       </c>
       <c r="N45">
-        <v>84.01885250000001</v>
+        <v>83.73557000000001</v>
       </c>
       <c r="O45">
-        <v>18.9042418125</v>
+        <v>18.84050325</v>
       </c>
       <c r="P45">
-        <v>65.1146106875</v>
+        <v>64.89506675000001</v>
       </c>
       <c r="Q45">
-        <v>86.4146106875</v>
+        <v>86.19506675000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2274613137256621</v>
+        <v>0.2302446658694561</v>
       </c>
       <c r="T45">
-        <v>1.266623074390061</v>
+        <v>1.286029837322572</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.897449727129567</v>
+        <v>7.717962233331169</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5008,22 +5008,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1471805128868954</v>
+        <v>0.1471582019501634</v>
       </c>
       <c r="C46">
-        <v>467.6386378664521</v>
+        <v>462.4936535427227</v>
       </c>
       <c r="D46">
-        <v>681.5186378664521</v>
+        <v>681.6686535427226</v>
       </c>
       <c r="E46">
-        <v>-123.92</v>
+        <v>-118.625</v>
       </c>
       <c r="F46">
-        <v>232.98</v>
+        <v>238.275</v>
       </c>
       <c r="G46">
         <v>19.1</v>
@@ -5044,45 +5044,45 @@
         <v>96.2</v>
       </c>
       <c r="M46">
-        <v>12.46443</v>
+        <v>12.9383325</v>
       </c>
       <c r="N46">
-        <v>83.73557000000001</v>
+        <v>83.2616675</v>
       </c>
       <c r="O46">
-        <v>18.84050325</v>
+        <v>18.7338751875</v>
       </c>
       <c r="P46">
-        <v>64.89506675000001</v>
+        <v>64.5277923125</v>
       </c>
       <c r="Q46">
-        <v>86.19506675000001</v>
+        <v>85.82779231249999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2302446658694561</v>
+        <v>0.2331292308184789</v>
       </c>
       <c r="T46">
-        <v>1.286029837322572</v>
+        <v>1.306142300725357</v>
       </c>
       <c r="U46">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V46">
         <v>0.225</v>
       </c>
       <c r="W46">
-        <v>0.0414625</v>
+        <v>0.0420825</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y46">
-        <v>7.717962233331169</v>
+        <v>7.435270348787218</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5090,22 +5090,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1471582019501634</v>
+        <v>0.1468630910134315</v>
       </c>
       <c r="C47">
-        <v>462.4936535427227</v>
+        <v>459.1891712764528</v>
       </c>
       <c r="D47">
-        <v>681.6686535427226</v>
+        <v>683.6591712764529</v>
       </c>
       <c r="E47">
-        <v>-118.625</v>
+        <v>-113.33</v>
       </c>
       <c r="F47">
-        <v>238.275</v>
+        <v>243.57</v>
       </c>
       <c r="G47">
         <v>19.1</v>
@@ -5126,28 +5126,28 @@
         <v>96.2</v>
       </c>
       <c r="M47">
-        <v>12.9383325</v>
+        <v>13.225851</v>
       </c>
       <c r="N47">
-        <v>83.2616675</v>
+        <v>82.974149</v>
       </c>
       <c r="O47">
-        <v>18.7338751875</v>
+        <v>18.669183525</v>
       </c>
       <c r="P47">
-        <v>64.5277923125</v>
+        <v>64.30496547499999</v>
       </c>
       <c r="Q47">
-        <v>85.82779231249999</v>
+        <v>85.60496547499999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2331292308184789</v>
+        <v>0.2361206315063545</v>
       </c>
       <c r="T47">
-        <v>1.306142300725357</v>
+        <v>1.326999670180096</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.435270348787218</v>
+        <v>7.27363403685706</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5172,22 +5172,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1468630910134315</v>
+        <v>0.1465679800766995</v>
       </c>
       <c r="C48">
-        <v>459.1891712764528</v>
+        <v>455.8963479429617</v>
       </c>
       <c r="D48">
-        <v>683.6591712764529</v>
+        <v>685.6613479429617</v>
       </c>
       <c r="E48">
-        <v>-113.33</v>
+        <v>-108.035</v>
       </c>
       <c r="F48">
-        <v>243.57</v>
+        <v>248.865</v>
       </c>
       <c r="G48">
         <v>19.1</v>
@@ -5208,28 +5208,28 @@
         <v>96.2</v>
       </c>
       <c r="M48">
-        <v>13.225851</v>
+        <v>13.5133695</v>
       </c>
       <c r="N48">
-        <v>82.974149</v>
+        <v>82.68663050000001</v>
       </c>
       <c r="O48">
-        <v>18.669183525</v>
+        <v>18.6044918625</v>
       </c>
       <c r="P48">
-        <v>64.30496547499999</v>
+        <v>64.08213863750001</v>
       </c>
       <c r="Q48">
-        <v>85.60496547499999</v>
+        <v>85.38213863750001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2361206315063545</v>
+        <v>0.2392249152390556</v>
       </c>
       <c r="T48">
-        <v>1.326999670180096</v>
+        <v>1.348644110180298</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.27363403685706</v>
+        <v>7.118875865860103</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5254,22 +5254,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1465679800766995</v>
+        <v>0.1462728691399675</v>
       </c>
       <c r="C49">
-        <v>455.8963479429617</v>
+        <v>452.6152862768066</v>
       </c>
       <c r="D49">
-        <v>685.6613479429617</v>
+        <v>687.6752862768066</v>
       </c>
       <c r="E49">
-        <v>-108.035</v>
+        <v>-102.74</v>
       </c>
       <c r="F49">
-        <v>248.865</v>
+        <v>254.16</v>
       </c>
       <c r="G49">
         <v>19.1</v>
@@ -5290,28 +5290,28 @@
         <v>96.2</v>
       </c>
       <c r="M49">
-        <v>13.5133695</v>
+        <v>13.800888</v>
       </c>
       <c r="N49">
-        <v>82.68663050000001</v>
+        <v>82.399112</v>
       </c>
       <c r="O49">
-        <v>18.6044918625</v>
+        <v>18.5398002</v>
       </c>
       <c r="P49">
-        <v>64.08213863750001</v>
+        <v>63.8593118</v>
       </c>
       <c r="Q49">
-        <v>85.38213863750001</v>
+        <v>85.1593118</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2392249152390556</v>
+        <v>0.2424485944999375</v>
       </c>
       <c r="T49">
-        <v>1.348644110180298</v>
+        <v>1.371121028642046</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.118875865860103</v>
+        <v>6.970565951988016</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5336,22 +5336,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1462728691399675</v>
+        <v>0.1459777582032355</v>
       </c>
       <c r="C50">
-        <v>452.6152862768066</v>
+        <v>449.3460902231165</v>
       </c>
       <c r="D50">
-        <v>687.6752862768066</v>
+        <v>689.7010902231165</v>
       </c>
       <c r="E50">
-        <v>-102.74</v>
+        <v>-97.44499999999999</v>
       </c>
       <c r="F50">
-        <v>254.16</v>
+        <v>259.455</v>
       </c>
       <c r="G50">
         <v>19.1</v>
@@ -5372,28 +5372,28 @@
         <v>96.2</v>
       </c>
       <c r="M50">
-        <v>13.800888</v>
+        <v>14.0884065</v>
       </c>
       <c r="N50">
-        <v>82.399112</v>
+        <v>82.1115935</v>
       </c>
       <c r="O50">
-        <v>18.5398002</v>
+        <v>18.4751085375</v>
       </c>
       <c r="P50">
-        <v>63.8593118</v>
+        <v>63.6364849625</v>
       </c>
       <c r="Q50">
-        <v>85.1593118</v>
+        <v>84.9364849625</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2424485944999375</v>
+        <v>0.2457986925553637</v>
       </c>
       <c r="T50">
-        <v>1.371121028642046</v>
+        <v>1.394479394886607</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.970565951988017</v>
+        <v>6.828309503988262</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5418,22 +5418,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1459777582032355</v>
+        <v>0.1456826472665035</v>
       </c>
       <c r="C51">
-        <v>449.3460902231165</v>
+        <v>446.0888649554755</v>
       </c>
       <c r="D51">
-        <v>689.7010902231165</v>
+        <v>691.7388649554755</v>
       </c>
       <c r="E51">
-        <v>-97.44499999999999</v>
+        <v>-92.14999999999998</v>
       </c>
       <c r="F51">
-        <v>259.455</v>
+        <v>264.75</v>
       </c>
       <c r="G51">
         <v>19.1</v>
@@ -5454,28 +5454,28 @@
         <v>96.2</v>
       </c>
       <c r="M51">
-        <v>14.0884065</v>
+        <v>14.375925</v>
       </c>
       <c r="N51">
-        <v>82.1115935</v>
+        <v>81.82407500000001</v>
       </c>
       <c r="O51">
-        <v>18.4751085375</v>
+        <v>18.410416875</v>
       </c>
       <c r="P51">
-        <v>63.6364849625</v>
+        <v>63.413658125</v>
       </c>
       <c r="Q51">
-        <v>84.9364849625</v>
+        <v>84.71365812499999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2457986925553637</v>
+        <v>0.249282794533007</v>
       </c>
       <c r="T51">
-        <v>1.394479394886607</v>
+        <v>1.418772095780951</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.828309503988262</v>
+        <v>6.691743313908496</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5500,22 +5500,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1456826472665035</v>
+        <v>0.1453875363297715</v>
       </c>
       <c r="C52">
-        <v>446.0888649554755</v>
+        <v>442.8437168941253</v>
       </c>
       <c r="D52">
-        <v>691.7388649554755</v>
+        <v>693.7887168941253</v>
       </c>
       <c r="E52">
-        <v>-92.14999999999998</v>
+        <v>-86.85499999999996</v>
       </c>
       <c r="F52">
-        <v>264.75</v>
+        <v>270.045</v>
       </c>
       <c r="G52">
         <v>19.1</v>
@@ -5536,28 +5536,28 @@
         <v>96.2</v>
       </c>
       <c r="M52">
-        <v>14.375925</v>
+        <v>14.6634435</v>
       </c>
       <c r="N52">
-        <v>81.82407500000001</v>
+        <v>81.5365565</v>
       </c>
       <c r="O52">
-        <v>18.410416875</v>
+        <v>18.3457252125</v>
       </c>
       <c r="P52">
-        <v>63.413658125</v>
+        <v>63.1908312875</v>
       </c>
       <c r="Q52">
-        <v>84.71365812499999</v>
+        <v>84.4908312875</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.249282794533007</v>
+        <v>0.2529091047546358</v>
       </c>
       <c r="T52">
-        <v>1.418772095780951</v>
+        <v>1.444056335487309</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.691743313908496</v>
+        <v>6.560532660694604</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5582,22 +5582,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1453875363297715</v>
+        <v>0.1450924253930395</v>
       </c>
       <c r="C53">
-        <v>442.8437168941253</v>
+        <v>439.6107537244901</v>
       </c>
       <c r="D53">
-        <v>693.7887168941253</v>
+        <v>695.8507537244901</v>
       </c>
       <c r="E53">
-        <v>-86.85499999999996</v>
+        <v>-81.55999999999995</v>
       </c>
       <c r="F53">
-        <v>270.045</v>
+        <v>275.34</v>
       </c>
       <c r="G53">
         <v>19.1</v>
@@ -5618,28 +5618,28 @@
         <v>96.2</v>
       </c>
       <c r="M53">
-        <v>14.6634435</v>
+        <v>14.950962</v>
       </c>
       <c r="N53">
-        <v>81.5365565</v>
+        <v>81.249038</v>
       </c>
       <c r="O53">
-        <v>18.3457252125</v>
+        <v>18.28103355</v>
       </c>
       <c r="P53">
-        <v>63.1908312875</v>
+        <v>62.96800445</v>
       </c>
       <c r="Q53">
-        <v>84.4908312875</v>
+        <v>84.26800444999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2529091047546358</v>
+        <v>0.2566865112354991</v>
       </c>
       <c r="T53">
-        <v>1.444056335487309</v>
+        <v>1.470394085181432</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5656,7 +5656,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.560532660694604</v>
+        <v>6.434368571065861</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5664,22 +5664,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1450924253930395</v>
+        <v>0.1447973144563076</v>
       </c>
       <c r="C54">
-        <v>439.6107537244901</v>
+        <v>436.3900844160356</v>
       </c>
       <c r="D54">
-        <v>695.8507537244901</v>
+        <v>697.9250844160356</v>
       </c>
       <c r="E54">
-        <v>-81.55999999999995</v>
+        <v>-76.26499999999999</v>
       </c>
       <c r="F54">
-        <v>275.34</v>
+        <v>280.635</v>
       </c>
       <c r="G54">
         <v>19.1</v>
@@ -5700,28 +5700,28 @@
         <v>96.2</v>
       </c>
       <c r="M54">
-        <v>14.950962</v>
+        <v>15.2384805</v>
       </c>
       <c r="N54">
-        <v>81.249038</v>
+        <v>80.96151950000001</v>
       </c>
       <c r="O54">
-        <v>18.28103355</v>
+        <v>18.2163418875</v>
       </c>
       <c r="P54">
-        <v>62.96800445</v>
+        <v>62.7451776125</v>
       </c>
       <c r="Q54">
-        <v>84.26800444999999</v>
+        <v>84.0451776125</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2566865112354991</v>
+        <v>0.2606246584176757</v>
       </c>
       <c r="T54">
-        <v>1.470394085181432</v>
+        <v>1.497852590181687</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.434368571065861</v>
+        <v>6.312965390479715</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5746,22 +5746,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1447973144563076</v>
+        <v>0.1445022035195756</v>
       </c>
       <c r="C55">
-        <v>436.3900844160356</v>
+        <v>433.1818192414632</v>
       </c>
       <c r="D55">
-        <v>697.9250844160356</v>
+        <v>700.0118192414632</v>
       </c>
       <c r="E55">
-        <v>-76.26499999999999</v>
+        <v>-70.96999999999997</v>
       </c>
       <c r="F55">
-        <v>280.635</v>
+        <v>285.93</v>
       </c>
       <c r="G55">
         <v>19.1</v>
@@ -5782,28 +5782,28 @@
         <v>96.2</v>
       </c>
       <c r="M55">
-        <v>15.2384805</v>
+        <v>15.525999</v>
       </c>
       <c r="N55">
-        <v>80.96151950000001</v>
+        <v>80.674001</v>
       </c>
       <c r="O55">
-        <v>18.2163418875</v>
+        <v>18.151650225</v>
       </c>
       <c r="P55">
-        <v>62.7451776125</v>
+        <v>62.52235077500001</v>
       </c>
       <c r="Q55">
-        <v>84.0451776125</v>
+        <v>83.822350775</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2606246584176757</v>
+        <v>0.2647340293903818</v>
       </c>
       <c r="T55">
-        <v>1.497852590181687</v>
+        <v>1.526504943225432</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.312965390479715</v>
+        <v>6.196058623989349</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5828,22 +5828,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1445022035195756</v>
+        <v>0.1446333425828436</v>
       </c>
       <c r="C56">
-        <v>433.1818192414632</v>
+        <v>426.9579940914393</v>
       </c>
       <c r="D56">
-        <v>700.0118192414632</v>
+        <v>699.0829940914393</v>
       </c>
       <c r="E56">
-        <v>-70.96999999999997</v>
+        <v>-65.67499999999995</v>
       </c>
       <c r="F56">
-        <v>285.93</v>
+        <v>291.225</v>
       </c>
       <c r="G56">
         <v>19.1</v>
@@ -5864,45 +5864,45 @@
         <v>96.2</v>
       </c>
       <c r="M56">
-        <v>15.525999</v>
+        <v>16.1047425</v>
       </c>
       <c r="N56">
-        <v>80.674001</v>
+        <v>80.0952575</v>
       </c>
       <c r="O56">
-        <v>18.151650225</v>
+        <v>18.0214329375</v>
       </c>
       <c r="P56">
-        <v>62.52235077500001</v>
+        <v>62.0738245625</v>
       </c>
       <c r="Q56">
-        <v>83.822350775</v>
+        <v>83.3738245625</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2647340293903818</v>
+        <v>0.2690260390729858</v>
       </c>
       <c r="T56">
-        <v>1.526504943225432</v>
+        <v>1.556430734182233</v>
       </c>
       <c r="U56">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V56">
         <v>0.225</v>
       </c>
       <c r="W56">
-        <v>0.0420825</v>
+        <v>0.0428575</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>6.196058623989349</v>
+        <v>5.973395724892838</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5910,22 +5910,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1446333425828436</v>
+        <v>0.1443459816461116</v>
       </c>
       <c r="C57">
-        <v>426.9579940914393</v>
+        <v>423.7015261622542</v>
       </c>
       <c r="D57">
-        <v>699.0829940914393</v>
+        <v>701.1215261622542</v>
       </c>
       <c r="E57">
-        <v>-65.67499999999995</v>
+        <v>-60.37999999999994</v>
       </c>
       <c r="F57">
-        <v>291.225</v>
+        <v>296.52</v>
       </c>
       <c r="G57">
         <v>19.1</v>
@@ -5946,28 +5946,28 @@
         <v>96.2</v>
       </c>
       <c r="M57">
-        <v>16.1047425</v>
+        <v>16.397556</v>
       </c>
       <c r="N57">
-        <v>80.0952575</v>
+        <v>79.80244400000001</v>
       </c>
       <c r="O57">
-        <v>18.0214329375</v>
+        <v>17.9555499</v>
       </c>
       <c r="P57">
-        <v>62.0738245625</v>
+        <v>61.84689410000001</v>
       </c>
       <c r="Q57">
-        <v>83.3738245625</v>
+        <v>83.1468941</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2690260390729858</v>
+        <v>0.2735131401047992</v>
       </c>
       <c r="T57">
-        <v>1.556430734182233</v>
+        <v>1.587716788364342</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.973395724892838</v>
+        <v>5.86672794409118</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5992,22 +5992,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1443459816461116</v>
+        <v>0.1440586207093797</v>
       </c>
       <c r="C58">
-        <v>423.7015261622542</v>
+        <v>420.4569817565457</v>
       </c>
       <c r="D58">
-        <v>701.1215261622542</v>
+        <v>703.1719817565457</v>
       </c>
       <c r="E58">
-        <v>-60.37999999999994</v>
+        <v>-55.08499999999992</v>
       </c>
       <c r="F58">
-        <v>296.52</v>
+        <v>301.8150000000001</v>
       </c>
       <c r="G58">
         <v>19.1</v>
@@ -6028,28 +6028,28 @@
         <v>96.2</v>
       </c>
       <c r="M58">
-        <v>16.397556</v>
+        <v>16.6903695</v>
       </c>
       <c r="N58">
-        <v>79.80244400000001</v>
+        <v>79.5096305</v>
       </c>
       <c r="O58">
-        <v>17.9555499</v>
+        <v>17.8896668625</v>
       </c>
       <c r="P58">
-        <v>61.84689410000001</v>
+        <v>61.6199636375</v>
       </c>
       <c r="Q58">
-        <v>83.1468941</v>
+        <v>82.91996363749999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2735131401047992</v>
+        <v>0.2782089435101853</v>
       </c>
       <c r="T58">
-        <v>1.587716788364342</v>
+        <v>1.620458007857247</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.86672794409118</v>
+        <v>5.763802892440457</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6074,22 +6074,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1440586207093797</v>
+        <v>0.1437712597726477</v>
       </c>
       <c r="C59">
-        <v>420.4569817565457</v>
+        <v>417.2244657934989</v>
       </c>
       <c r="D59">
-        <v>703.1719817565457</v>
+        <v>705.2344657934989</v>
       </c>
       <c r="E59">
-        <v>-55.08499999999992</v>
+        <v>-49.78999999999996</v>
       </c>
       <c r="F59">
-        <v>301.8150000000001</v>
+        <v>307.11</v>
       </c>
       <c r="G59">
         <v>19.1</v>
@@ -6110,28 +6110,28 @@
         <v>96.2</v>
       </c>
       <c r="M59">
-        <v>16.6903695</v>
+        <v>16.983183</v>
       </c>
       <c r="N59">
-        <v>79.5096305</v>
+        <v>79.21681700000001</v>
       </c>
       <c r="O59">
-        <v>17.8896668625</v>
+        <v>17.823783825</v>
       </c>
       <c r="P59">
-        <v>61.6199636375</v>
+        <v>61.393033175</v>
       </c>
       <c r="Q59">
-        <v>82.91996363749999</v>
+        <v>82.693033175</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2782089435101853</v>
+        <v>0.2831283566015421</v>
       </c>
       <c r="T59">
-        <v>1.620458007857247</v>
+        <v>1.654758333040291</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.763802892440457</v>
+        <v>5.66442698050183</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6156,22 +6156,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1437712597726477</v>
+        <v>0.1434838988359157</v>
       </c>
       <c r="C60">
-        <v>417.2244657934987</v>
+        <v>414.0040844268777</v>
       </c>
       <c r="D60">
-        <v>705.2344657934987</v>
+        <v>707.3090844268777</v>
       </c>
       <c r="E60">
-        <v>-49.79000000000002</v>
+        <v>-44.495</v>
       </c>
       <c r="F60">
-        <v>307.11</v>
+        <v>312.405</v>
       </c>
       <c r="G60">
         <v>19.1</v>
@@ -6192,28 +6192,28 @@
         <v>96.2</v>
       </c>
       <c r="M60">
-        <v>16.983183</v>
+        <v>17.2759965</v>
       </c>
       <c r="N60">
-        <v>79.21681700000001</v>
+        <v>78.9240035</v>
       </c>
       <c r="O60">
-        <v>17.823783825</v>
+        <v>17.7579007875</v>
       </c>
       <c r="P60">
-        <v>61.393033175</v>
+        <v>61.1661027125</v>
       </c>
       <c r="Q60">
-        <v>82.693033175</v>
+        <v>82.4661027125</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2831283566015421</v>
+        <v>0.288287741063209</v>
       </c>
       <c r="T60">
-        <v>1.654758333040291</v>
+        <v>1.690731844817629</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.664426980501831</v>
+        <v>5.568419743544172</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6238,22 +6238,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1434838988359157</v>
+        <v>0.1431965378991837</v>
       </c>
       <c r="C61">
-        <v>414.0040844268777</v>
+        <v>410.795945063242</v>
       </c>
       <c r="D61">
-        <v>707.3090844268777</v>
+        <v>709.3959450632419</v>
       </c>
       <c r="E61">
-        <v>-44.495</v>
+        <v>-39.19999999999999</v>
       </c>
       <c r="F61">
-        <v>312.405</v>
+        <v>317.7</v>
       </c>
       <c r="G61">
         <v>19.1</v>
@@ -6274,28 +6274,28 @@
         <v>96.2</v>
       </c>
       <c r="M61">
-        <v>17.2759965</v>
+        <v>17.56881</v>
       </c>
       <c r="N61">
-        <v>78.9240035</v>
+        <v>78.63119</v>
       </c>
       <c r="O61">
-        <v>17.7579007875</v>
+        <v>17.69201775</v>
       </c>
       <c r="P61">
-        <v>61.1661027125</v>
+        <v>60.93917225</v>
       </c>
       <c r="Q61">
-        <v>82.4661027125</v>
+        <v>82.23917225</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.288287741063209</v>
+        <v>0.2937050947479592</v>
       </c>
       <c r="T61">
-        <v>1.690731844817629</v>
+        <v>1.728504032183834</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.568419743544172</v>
+        <v>5.475612747818436</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6320,22 +6320,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1431965378991837</v>
+        <v>0.1429091769624517</v>
       </c>
       <c r="C62">
-        <v>410.795945063242</v>
+        <v>407.6001563804797</v>
       </c>
       <c r="D62">
-        <v>709.3959450632419</v>
+        <v>711.4951563804797</v>
       </c>
       <c r="E62">
-        <v>-39.19999999999999</v>
+        <v>-33.90499999999997</v>
       </c>
       <c r="F62">
-        <v>317.7</v>
+        <v>322.995</v>
       </c>
       <c r="G62">
         <v>19.1</v>
@@ -6356,28 +6356,28 @@
         <v>96.2</v>
       </c>
       <c r="M62">
-        <v>17.56881</v>
+        <v>17.8616235</v>
       </c>
       <c r="N62">
-        <v>78.63119</v>
+        <v>78.33837650000001</v>
       </c>
       <c r="O62">
-        <v>17.69201775</v>
+        <v>17.6261347125</v>
       </c>
       <c r="P62">
-        <v>60.93917225</v>
+        <v>60.71224178750001</v>
       </c>
       <c r="Q62">
-        <v>82.23917225</v>
+        <v>82.0122417875</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2937050947479592</v>
+        <v>0.2994002614421839</v>
       </c>
       <c r="T62">
-        <v>1.728504032183834</v>
+        <v>1.768213254799589</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.475612747818436</v>
+        <v>5.385848604411576</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6402,22 +6402,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1429091769624517</v>
+        <v>0.1426218160257197</v>
       </c>
       <c r="C63">
-        <v>407.6001563804797</v>
+        <v>404.4168283466764</v>
       </c>
       <c r="D63">
-        <v>711.4951563804797</v>
+        <v>713.6068283466764</v>
       </c>
       <c r="E63">
-        <v>-33.90499999999997</v>
+        <v>-28.60999999999996</v>
       </c>
       <c r="F63">
-        <v>322.995</v>
+        <v>328.29</v>
       </c>
       <c r="G63">
         <v>19.1</v>
@@ -6438,28 +6438,28 @@
         <v>96.2</v>
       </c>
       <c r="M63">
-        <v>17.8616235</v>
+        <v>18.154437</v>
       </c>
       <c r="N63">
-        <v>78.33837650000001</v>
+        <v>78.045563</v>
       </c>
       <c r="O63">
-        <v>17.6261347125</v>
+        <v>17.560251675</v>
       </c>
       <c r="P63">
-        <v>60.71224178750001</v>
+        <v>60.485311325</v>
       </c>
       <c r="Q63">
-        <v>82.0122417875</v>
+        <v>81.785311325</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2994002614421839</v>
+        <v>0.3053951737518941</v>
       </c>
       <c r="T63">
-        <v>1.768213254799589</v>
+        <v>1.810012436500383</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.385848604411576</v>
+        <v>5.298980078533969</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6484,22 +6484,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1426218160257197</v>
+        <v>0.1423344550889878</v>
       </c>
       <c r="C64">
-        <v>404.4168283466764</v>
+        <v>401.2460722393157</v>
       </c>
       <c r="D64">
-        <v>713.6068283466764</v>
+        <v>715.7310722393156</v>
       </c>
       <c r="E64">
-        <v>-28.60999999999996</v>
+        <v>-23.315</v>
       </c>
       <c r="F64">
-        <v>328.29</v>
+        <v>333.585</v>
       </c>
       <c r="G64">
         <v>19.1</v>
@@ -6520,28 +6520,28 @@
         <v>96.2</v>
       </c>
       <c r="M64">
-        <v>18.154437</v>
+        <v>18.4472505</v>
       </c>
       <c r="N64">
-        <v>78.045563</v>
+        <v>77.75274950000001</v>
       </c>
       <c r="O64">
-        <v>17.560251675</v>
+        <v>17.4943686375</v>
       </c>
       <c r="P64">
-        <v>60.485311325</v>
+        <v>60.2583808625</v>
       </c>
       <c r="Q64">
-        <v>81.785311325</v>
+        <v>81.5583808625</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3053951737518941</v>
+        <v>0.3117141353756426</v>
       </c>
       <c r="T64">
-        <v>1.810012436500383</v>
+        <v>1.854071033428247</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.298980078533969</v>
+        <v>5.214869283636605</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6566,22 +6566,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1423344550889878</v>
+        <v>0.1420470941522558</v>
       </c>
       <c r="C65">
-        <v>401.2460722393157</v>
+        <v>398.0880006648274</v>
       </c>
       <c r="D65">
-        <v>715.7310722393156</v>
+        <v>717.8680006648274</v>
       </c>
       <c r="E65">
-        <v>-23.315</v>
+        <v>-18.01999999999998</v>
       </c>
       <c r="F65">
-        <v>333.585</v>
+        <v>338.88</v>
       </c>
       <c r="G65">
         <v>19.1</v>
@@ -6602,28 +6602,28 @@
         <v>96.2</v>
       </c>
       <c r="M65">
-        <v>18.4472505</v>
+        <v>18.740064</v>
       </c>
       <c r="N65">
-        <v>77.75274950000001</v>
+        <v>77.459936</v>
       </c>
       <c r="O65">
-        <v>17.4943686375</v>
+        <v>17.4284856</v>
       </c>
       <c r="P65">
-        <v>60.2583808625</v>
+        <v>60.0314504</v>
       </c>
       <c r="Q65">
-        <v>81.5583808625</v>
+        <v>81.33145039999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3117141353756426</v>
+        <v>0.3183841504229328</v>
       </c>
       <c r="T65">
-        <v>1.854071033428247</v>
+        <v>1.900577330185437</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.214869283636605</v>
+        <v>5.133386951079783</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6648,22 +6648,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1420470941522558</v>
+        <v>0.1417597332155238</v>
       </c>
       <c r="C66">
-        <v>398.0880006648274</v>
+        <v>394.9427275784865</v>
       </c>
       <c r="D66">
-        <v>717.8680006648274</v>
+        <v>720.0177275784865</v>
       </c>
       <c r="E66">
-        <v>-18.01999999999998</v>
+        <v>-12.72499999999997</v>
       </c>
       <c r="F66">
-        <v>338.88</v>
+        <v>344.175</v>
       </c>
       <c r="G66">
         <v>19.1</v>
@@ -6684,28 +6684,28 @@
         <v>96.2</v>
       </c>
       <c r="M66">
-        <v>18.740064</v>
+        <v>19.0328775</v>
       </c>
       <c r="N66">
-        <v>77.459936</v>
+        <v>77.1671225</v>
       </c>
       <c r="O66">
-        <v>17.4284856</v>
+        <v>17.3626025625</v>
       </c>
       <c r="P66">
-        <v>60.0314504</v>
+        <v>59.8045199375</v>
       </c>
       <c r="Q66">
-        <v>81.33145039999999</v>
+        <v>81.1045199375</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3183841504229328</v>
+        <v>0.3254353091872109</v>
       </c>
       <c r="T66">
-        <v>1.900577330185437</v>
+        <v>1.949741129614466</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.133386951079783</v>
+        <v>5.054411767217017</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6730,22 +6730,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1417597332155238</v>
+        <v>0.1414723722787918</v>
       </c>
       <c r="C67">
-        <v>394.9427275784865</v>
+        <v>391.8103683046687</v>
       </c>
       <c r="D67">
-        <v>720.0177275784865</v>
+        <v>722.1803683046687</v>
       </c>
       <c r="E67">
-        <v>-12.72499999999997</v>
+        <v>-7.42999999999995</v>
       </c>
       <c r="F67">
-        <v>344.175</v>
+        <v>349.47</v>
       </c>
       <c r="G67">
         <v>19.1</v>
@@ -6766,28 +6766,28 @@
         <v>96.2</v>
       </c>
       <c r="M67">
-        <v>19.0328775</v>
+        <v>19.325691</v>
       </c>
       <c r="N67">
-        <v>77.1671225</v>
+        <v>76.874309</v>
       </c>
       <c r="O67">
-        <v>17.3626025625</v>
+        <v>17.296719525</v>
       </c>
       <c r="P67">
-        <v>59.8045199375</v>
+        <v>59.577589475</v>
       </c>
       <c r="Q67">
-        <v>81.1045199375</v>
+        <v>80.87758947499999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3254353091872109</v>
+        <v>0.3329012419964466</v>
       </c>
       <c r="T67">
-        <v>1.949741129614466</v>
+        <v>2.001796917245203</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6804,7 +6804,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.054411767217017</v>
+        <v>4.977829770744031</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6812,22 +6812,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1414723722787918</v>
+        <v>0.1411850113420599</v>
       </c>
       <c r="C68">
-        <v>391.8103683046687</v>
+        <v>388.6910395574747</v>
       </c>
       <c r="D68">
-        <v>722.1803683046687</v>
+        <v>724.3560395574747</v>
       </c>
       <c r="E68">
-        <v>-7.42999999999995</v>
+        <v>-2.134999999999934</v>
       </c>
       <c r="F68">
-        <v>349.47</v>
+        <v>354.765</v>
       </c>
       <c r="G68">
         <v>19.1</v>
@@ -6848,28 +6848,28 @@
         <v>96.2</v>
       </c>
       <c r="M68">
-        <v>19.325691</v>
+        <v>19.6185045</v>
       </c>
       <c r="N68">
-        <v>76.874309</v>
+        <v>76.5814955</v>
       </c>
       <c r="O68">
-        <v>17.296719525</v>
+        <v>17.2308364875</v>
       </c>
       <c r="P68">
-        <v>59.577589475</v>
+        <v>59.3506590125</v>
       </c>
       <c r="Q68">
-        <v>80.87758947499999</v>
+        <v>80.6506590125</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3329012419964466</v>
+        <v>0.3408196555819996</v>
       </c>
       <c r="T68">
-        <v>2.001796917245203</v>
+        <v>2.057007601095984</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.977829770744031</v>
+        <v>4.903533804016508</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6894,22 +6894,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1411850113420599</v>
+        <v>0.1408976504053279</v>
       </c>
       <c r="C69">
-        <v>388.6910395574747</v>
+        <v>385.5848594617259</v>
       </c>
       <c r="D69">
-        <v>724.3560395574747</v>
+        <v>726.5448594617259</v>
       </c>
       <c r="E69">
-        <v>-2.134999999999934</v>
+        <v>3.160000000000025</v>
       </c>
       <c r="F69">
-        <v>354.765</v>
+        <v>360.06</v>
       </c>
       <c r="G69">
         <v>19.1</v>
@@ -6930,28 +6930,28 @@
         <v>96.2</v>
       </c>
       <c r="M69">
-        <v>19.6185045</v>
+        <v>19.911318</v>
       </c>
       <c r="N69">
-        <v>76.5814955</v>
+        <v>76.28868199999999</v>
       </c>
       <c r="O69">
-        <v>17.2308364875</v>
+        <v>17.16495345</v>
       </c>
       <c r="P69">
-        <v>59.3506590125</v>
+        <v>59.12372855</v>
       </c>
       <c r="Q69">
-        <v>80.6506590125</v>
+        <v>80.42372854999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3408196555819996</v>
+        <v>0.3492329700166497</v>
       </c>
       <c r="T69">
-        <v>2.057007601095984</v>
+        <v>2.115668952687439</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.903533804016508</v>
+        <v>4.831423012780972</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6976,22 +6976,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1408976504053279</v>
+        <v>0.1406102894685959</v>
       </c>
       <c r="C70">
-        <v>385.5848594617259</v>
+        <v>382.4919475743445</v>
       </c>
       <c r="D70">
-        <v>726.5448594617259</v>
+        <v>728.7469475743445</v>
       </c>
       <c r="E70">
-        <v>3.160000000000025</v>
+        <v>8.455000000000041</v>
       </c>
       <c r="F70">
-        <v>360.06</v>
+        <v>365.355</v>
       </c>
       <c r="G70">
         <v>19.1</v>
@@ -7012,28 +7012,28 @@
         <v>96.2</v>
       </c>
       <c r="M70">
-        <v>19.911318</v>
+        <v>20.2041315</v>
       </c>
       <c r="N70">
-        <v>76.28868199999999</v>
+        <v>75.9958685</v>
       </c>
       <c r="O70">
-        <v>17.16495345</v>
+        <v>17.0990704125</v>
       </c>
       <c r="P70">
-        <v>59.12372855</v>
+        <v>58.8967980875</v>
       </c>
       <c r="Q70">
-        <v>80.42372854999999</v>
+        <v>80.1967980875</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3492329700166497</v>
+        <v>0.3581890789309545</v>
       </c>
       <c r="T70">
-        <v>2.115668952687439</v>
+        <v>2.178114907607376</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.831423012780972</v>
+        <v>4.761402389407334</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7058,22 +7058,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1406102894685959</v>
+        <v>0.1403229285318639</v>
       </c>
       <c r="C71">
-        <v>382.4919475743445</v>
+        <v>379.4124249061219</v>
       </c>
       <c r="D71">
-        <v>728.7469475743445</v>
+        <v>730.9624249061219</v>
       </c>
       <c r="E71">
-        <v>8.455000000000041</v>
+        <v>13.75000000000006</v>
       </c>
       <c r="F71">
-        <v>365.355</v>
+        <v>370.65</v>
       </c>
       <c r="G71">
         <v>19.1</v>
@@ -7094,28 +7094,28 @@
         <v>96.2</v>
       </c>
       <c r="M71">
-        <v>20.2041315</v>
+        <v>20.496945</v>
       </c>
       <c r="N71">
-        <v>75.9958685</v>
+        <v>75.70305500000001</v>
       </c>
       <c r="O71">
-        <v>17.0990704125</v>
+        <v>17.033187375</v>
       </c>
       <c r="P71">
-        <v>58.8967980875</v>
+        <v>58.66986762500001</v>
       </c>
       <c r="Q71">
-        <v>80.1967980875</v>
+        <v>79.96986762500001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3581890789309545</v>
+        <v>0.3677422617728797</v>
       </c>
       <c r="T71">
-        <v>2.178114907607376</v>
+        <v>2.24472392618864</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.761402389407334</v>
+        <v>4.693382355272944</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7140,22 +7140,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1403229285318639</v>
+        <v>0.1400355675951319</v>
       </c>
       <c r="C72">
-        <v>379.4124249061219</v>
+        <v>376.3464139438845</v>
       </c>
       <c r="D72">
-        <v>730.9624249061219</v>
+        <v>733.1914139438845</v>
       </c>
       <c r="E72">
-        <v>13.75000000000006</v>
+        <v>19.04500000000007</v>
       </c>
       <c r="F72">
-        <v>370.65</v>
+        <v>375.9450000000001</v>
       </c>
       <c r="G72">
         <v>19.1</v>
@@ -7176,28 +7176,28 @@
         <v>96.2</v>
       </c>
       <c r="M72">
-        <v>20.496945</v>
+        <v>20.7897585</v>
       </c>
       <c r="N72">
-        <v>75.70305500000001</v>
+        <v>75.4102415</v>
       </c>
       <c r="O72">
-        <v>17.033187375</v>
+        <v>16.9673043375</v>
       </c>
       <c r="P72">
-        <v>58.66986762500001</v>
+        <v>58.4429371625</v>
       </c>
       <c r="Q72">
-        <v>79.96986762500001</v>
+        <v>79.7429371625</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3677422617728797</v>
+        <v>0.3779542848107998</v>
       </c>
       <c r="T72">
-        <v>2.24472392618864</v>
+        <v>2.315926670189304</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.693382355272944</v>
+        <v>4.627278378438113</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7222,22 +7222,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1400355675951319</v>
+        <v>0.1397482066583999</v>
       </c>
       <c r="C73">
-        <v>376.3464139438843</v>
+        <v>373.2940386730701</v>
       </c>
       <c r="D73">
-        <v>733.1914139438843</v>
+        <v>735.4340386730701</v>
       </c>
       <c r="E73">
-        <v>19.04500000000002</v>
+        <v>24.34000000000003</v>
       </c>
       <c r="F73">
-        <v>375.945</v>
+        <v>381.24</v>
       </c>
       <c r="G73">
         <v>19.1</v>
@@ -7258,28 +7258,28 @@
         <v>96.2</v>
       </c>
       <c r="M73">
-        <v>20.7897585</v>
+        <v>21.082572</v>
       </c>
       <c r="N73">
-        <v>75.4102415</v>
+        <v>75.117428</v>
       </c>
       <c r="O73">
-        <v>16.9673043375</v>
+        <v>16.9014213</v>
       </c>
       <c r="P73">
-        <v>58.4429371625</v>
+        <v>58.2160067</v>
       </c>
       <c r="Q73">
-        <v>79.7429371625</v>
+        <v>79.51600669999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3779542848107997</v>
+        <v>0.388895738065714</v>
       </c>
       <c r="T73">
-        <v>2.315926670189303</v>
+        <v>2.392215324475728</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.627278378438113</v>
+        <v>4.563010623182029</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7304,22 +7304,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1397482066583999</v>
+        <v>0.1394608457216679</v>
       </c>
       <c r="C74">
-        <v>373.2940386730701</v>
+        <v>370.2554246007149</v>
       </c>
       <c r="D74">
-        <v>735.4340386730701</v>
+        <v>737.6904246007149</v>
       </c>
       <c r="E74">
-        <v>24.34000000000003</v>
+        <v>29.63499999999999</v>
       </c>
       <c r="F74">
-        <v>381.24</v>
+        <v>386.535</v>
       </c>
       <c r="G74">
         <v>19.1</v>
@@ -7340,28 +7340,28 @@
         <v>96.2</v>
       </c>
       <c r="M74">
-        <v>21.082572</v>
+        <v>21.3753855</v>
       </c>
       <c r="N74">
-        <v>75.117428</v>
+        <v>74.8246145</v>
       </c>
       <c r="O74">
-        <v>16.9014213</v>
+        <v>16.8355382625</v>
       </c>
       <c r="P74">
-        <v>58.2160067</v>
+        <v>57.9890762375</v>
       </c>
       <c r="Q74">
-        <v>79.51600669999999</v>
+        <v>79.2890762375</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.388895738065714</v>
+        <v>0.4006476693395109</v>
       </c>
       <c r="T74">
-        <v>2.392215324475728</v>
+        <v>2.474154990190776</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.563010623182029</v>
+        <v>4.500503628343919</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7386,22 +7386,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1394608457216679</v>
+        <v>0.140607234784936</v>
       </c>
       <c r="C75">
-        <v>370.2554246007149</v>
+        <v>356.0404277591428</v>
       </c>
       <c r="D75">
-        <v>737.6904246007149</v>
+        <v>728.7704277591428</v>
       </c>
       <c r="E75">
-        <v>29.63499999999999</v>
+        <v>34.93000000000001</v>
       </c>
       <c r="F75">
-        <v>386.535</v>
+        <v>391.83</v>
       </c>
       <c r="G75">
         <v>19.1</v>
@@ -7422,45 +7422,45 @@
         <v>96.2</v>
       </c>
       <c r="M75">
-        <v>21.3753855</v>
+        <v>22.647774</v>
       </c>
       <c r="N75">
-        <v>74.8246145</v>
+        <v>73.552226</v>
       </c>
       <c r="O75">
-        <v>16.8355382625</v>
+        <v>16.54925085</v>
       </c>
       <c r="P75">
-        <v>57.9890762375</v>
+        <v>57.00297515</v>
       </c>
       <c r="Q75">
-        <v>79.2890762375</v>
+        <v>78.30297515000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4006476693395109</v>
+        <v>0.4133035953266768</v>
       </c>
       <c r="T75">
-        <v>2.474154990190776</v>
+        <v>2.562397707114675</v>
       </c>
       <c r="U75">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V75">
         <v>0.225</v>
       </c>
       <c r="W75">
-        <v>0.0428575</v>
+        <v>0.044795</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>4.500503628343919</v>
+        <v>4.247658070060218</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7468,22 +7468,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.140607234784936</v>
+        <v>0.140339248848204</v>
       </c>
       <c r="C76">
-        <v>356.0404277591428</v>
+        <v>352.8112388177769</v>
       </c>
       <c r="D76">
-        <v>728.7704277591428</v>
+        <v>730.8362388177769</v>
       </c>
       <c r="E76">
-        <v>34.93000000000001</v>
+        <v>40.22500000000002</v>
       </c>
       <c r="F76">
-        <v>391.83</v>
+        <v>397.125</v>
       </c>
       <c r="G76">
         <v>19.1</v>
@@ -7504,28 +7504,28 @@
         <v>96.2</v>
       </c>
       <c r="M76">
-        <v>22.647774</v>
+        <v>22.953825</v>
       </c>
       <c r="N76">
-        <v>73.552226</v>
+        <v>73.24617499999999</v>
       </c>
       <c r="O76">
-        <v>16.54925085</v>
+        <v>16.480389375</v>
       </c>
       <c r="P76">
-        <v>57.00297515</v>
+        <v>56.76578562499999</v>
       </c>
       <c r="Q76">
-        <v>78.30297515000001</v>
+        <v>78.06578562499999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4133035953266768</v>
+        <v>0.426971995392816</v>
       </c>
       <c r="T76">
-        <v>2.562397707114675</v>
+        <v>2.657699841392485</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.247658070060218</v>
+        <v>4.191022629126082</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7550,22 +7550,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.140339248848204</v>
+        <v>0.140071262911472</v>
       </c>
       <c r="C77">
-        <v>352.8112388177769</v>
+        <v>349.5937948832048</v>
       </c>
       <c r="D77">
-        <v>730.8362388177769</v>
+        <v>732.9137948832048</v>
       </c>
       <c r="E77">
-        <v>40.22500000000002</v>
+        <v>45.52000000000004</v>
       </c>
       <c r="F77">
-        <v>397.125</v>
+        <v>402.42</v>
       </c>
       <c r="G77">
         <v>19.1</v>
@@ -7586,28 +7586,28 @@
         <v>96.2</v>
       </c>
       <c r="M77">
-        <v>22.953825</v>
+        <v>23.259876</v>
       </c>
       <c r="N77">
-        <v>73.24617499999999</v>
+        <v>72.940124</v>
       </c>
       <c r="O77">
-        <v>16.480389375</v>
+        <v>16.4115279</v>
       </c>
       <c r="P77">
-        <v>56.76578562499999</v>
+        <v>56.5285961</v>
       </c>
       <c r="Q77">
-        <v>78.06578562499999</v>
+        <v>77.8285961</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.426971995392816</v>
+        <v>0.4417794287978001</v>
       </c>
       <c r="T77">
-        <v>2.657699841392485</v>
+        <v>2.760943820193447</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7624,7 +7624,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.191022629126082</v>
+        <v>4.135877594532317</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7632,22 +7632,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.140071262911472</v>
+        <v>0.13980327697474</v>
       </c>
       <c r="C78">
-        <v>349.5937948832048</v>
+        <v>346.3881964039448</v>
       </c>
       <c r="D78">
-        <v>732.9137948832048</v>
+        <v>735.0031964039448</v>
       </c>
       <c r="E78">
-        <v>45.52000000000004</v>
+        <v>50.81500000000005</v>
       </c>
       <c r="F78">
-        <v>402.42</v>
+        <v>407.715</v>
       </c>
       <c r="G78">
         <v>19.1</v>
@@ -7668,28 +7668,28 @@
         <v>96.2</v>
       </c>
       <c r="M78">
-        <v>23.259876</v>
+        <v>23.565927</v>
       </c>
       <c r="N78">
-        <v>72.940124</v>
+        <v>72.634073</v>
       </c>
       <c r="O78">
-        <v>16.4115279</v>
+        <v>16.342666425</v>
       </c>
       <c r="P78">
-        <v>56.5285961</v>
+        <v>56.291406575</v>
       </c>
       <c r="Q78">
-        <v>77.8285961</v>
+        <v>77.59140657499999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4417794287978001</v>
+        <v>0.4578744651075655</v>
       </c>
       <c r="T78">
-        <v>2.760943820193447</v>
+        <v>2.873165536281448</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.135877594532317</v>
+        <v>4.08216489849943</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7714,22 +7714,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.13980327697474</v>
+        <v>0.139535291038008</v>
       </c>
       <c r="C79">
-        <v>346.3881964039448</v>
+        <v>343.1945449772313</v>
       </c>
       <c r="D79">
-        <v>735.0031964039448</v>
+        <v>737.1045449772313</v>
       </c>
       <c r="E79">
-        <v>50.81500000000005</v>
+        <v>56.11000000000001</v>
       </c>
       <c r="F79">
-        <v>407.715</v>
+        <v>413.01</v>
       </c>
       <c r="G79">
         <v>19.1</v>
@@ -7750,28 +7750,28 @@
         <v>96.2</v>
       </c>
       <c r="M79">
-        <v>23.565927</v>
+        <v>23.871978</v>
       </c>
       <c r="N79">
-        <v>72.634073</v>
+        <v>72.328022</v>
       </c>
       <c r="O79">
-        <v>16.342666425</v>
+        <v>16.27380495</v>
       </c>
       <c r="P79">
-        <v>56.291406575</v>
+        <v>56.05421705000001</v>
       </c>
       <c r="Q79">
-        <v>77.59140657499999</v>
+        <v>77.35421705</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4578744651075655</v>
+        <v>0.4754326865364003</v>
       </c>
       <c r="T79">
-        <v>2.873165536281448</v>
+        <v>2.995589226559268</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.08216489849943</v>
+        <v>4.029829451082771</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7796,22 +7796,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.139535291038008</v>
+        <v>0.1414101801012761</v>
       </c>
       <c r="C80">
-        <v>343.1945449772313</v>
+        <v>323.4451296796231</v>
       </c>
       <c r="D80">
-        <v>737.1045449772313</v>
+        <v>722.6501296796231</v>
       </c>
       <c r="E80">
-        <v>56.11000000000001</v>
+        <v>61.40500000000003</v>
       </c>
       <c r="F80">
-        <v>413.01</v>
+        <v>418.305</v>
       </c>
       <c r="G80">
         <v>19.1</v>
@@ -7832,45 +7832,45 @@
         <v>96.2</v>
       </c>
       <c r="M80">
-        <v>23.871978</v>
+        <v>25.6420965</v>
       </c>
       <c r="N80">
-        <v>72.328022</v>
+        <v>70.55790350000001</v>
       </c>
       <c r="O80">
-        <v>16.27380495</v>
+        <v>15.8755282875</v>
       </c>
       <c r="P80">
-        <v>56.05421705000001</v>
+        <v>54.68237521250001</v>
       </c>
       <c r="Q80">
-        <v>77.35421705</v>
+        <v>75.9823752125</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4754326865364003</v>
+        <v>0.4946631195298862</v>
       </c>
       <c r="T80">
-        <v>2.995589226559268</v>
+        <v>3.129672315911166</v>
       </c>
       <c r="U80">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V80">
         <v>0.225</v>
       </c>
       <c r="W80">
-        <v>0.044795</v>
+        <v>0.0475075</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>4.029829451082771</v>
+        <v>3.751643318244279</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7878,22 +7878,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1414101801012761</v>
+        <v>0.1411693191645441</v>
       </c>
       <c r="C81">
-        <v>323.4451296796231</v>
+        <v>319.975225933732</v>
       </c>
       <c r="D81">
-        <v>722.6501296796231</v>
+        <v>724.475225933732</v>
       </c>
       <c r="E81">
-        <v>61.40500000000003</v>
+        <v>66.70000000000005</v>
       </c>
       <c r="F81">
-        <v>418.305</v>
+        <v>423.6</v>
       </c>
       <c r="G81">
         <v>19.1</v>
@@ -7914,28 +7914,28 @@
         <v>96.2</v>
       </c>
       <c r="M81">
-        <v>25.6420965</v>
+        <v>25.96668</v>
       </c>
       <c r="N81">
-        <v>70.55790350000001</v>
+        <v>70.23332000000001</v>
       </c>
       <c r="O81">
-        <v>15.8755282875</v>
+        <v>15.802497</v>
       </c>
       <c r="P81">
-        <v>54.68237521250001</v>
+        <v>54.430823</v>
       </c>
       <c r="Q81">
-        <v>75.9823752125</v>
+        <v>75.730823</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4946631195298862</v>
+        <v>0.5158165958227205</v>
       </c>
       <c r="T81">
-        <v>3.129672315911166</v>
+        <v>3.277163714198254</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.751643318244279</v>
+        <v>3.704747776766225</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7960,22 +7960,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1411693191645441</v>
+        <v>0.1409284582278121</v>
       </c>
       <c r="C82">
-        <v>319.975225933732</v>
+        <v>316.5145643095272</v>
       </c>
       <c r="D82">
-        <v>724.475225933732</v>
+        <v>726.3095643095272</v>
       </c>
       <c r="E82">
-        <v>66.70000000000005</v>
+        <v>71.99500000000006</v>
       </c>
       <c r="F82">
-        <v>423.6</v>
+        <v>428.895</v>
       </c>
       <c r="G82">
         <v>19.1</v>
@@ -7996,28 +7996,28 @@
         <v>96.2</v>
       </c>
       <c r="M82">
-        <v>25.96668</v>
+        <v>26.2912635</v>
       </c>
       <c r="N82">
-        <v>70.23332000000001</v>
+        <v>69.9087365</v>
       </c>
       <c r="O82">
-        <v>15.802497</v>
+        <v>15.7294657125</v>
       </c>
       <c r="P82">
-        <v>54.430823</v>
+        <v>54.1792707875</v>
       </c>
       <c r="Q82">
-        <v>75.730823</v>
+        <v>75.4792707875</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5158165958227205</v>
+        <v>0.5391967538305902</v>
       </c>
       <c r="T82">
-        <v>3.277163714198254</v>
+        <v>3.44018052283135</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.704747776766225</v>
+        <v>3.659010149892568</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8042,22 +8042,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1409284582278121</v>
+        <v>0.1406875972910801</v>
       </c>
       <c r="C83">
-        <v>316.5145643095272</v>
+        <v>313.0632151871056</v>
       </c>
       <c r="D83">
-        <v>726.3095643095272</v>
+        <v>728.1532151871056</v>
       </c>
       <c r="E83">
-        <v>71.99500000000006</v>
+        <v>77.29000000000008</v>
       </c>
       <c r="F83">
-        <v>428.895</v>
+        <v>434.1900000000001</v>
       </c>
       <c r="G83">
         <v>19.1</v>
@@ -8078,28 +8078,28 @@
         <v>96.2</v>
       </c>
       <c r="M83">
-        <v>26.2912635</v>
+        <v>26.615847</v>
       </c>
       <c r="N83">
-        <v>69.9087365</v>
+        <v>69.584153</v>
       </c>
       <c r="O83">
-        <v>15.7294657125</v>
+        <v>15.656434425</v>
       </c>
       <c r="P83">
-        <v>54.1792707875</v>
+        <v>53.927718575</v>
       </c>
       <c r="Q83">
-        <v>75.4792707875</v>
+        <v>75.227718575</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5391967538305902</v>
+        <v>0.5651747071726675</v>
       </c>
       <c r="T83">
-        <v>3.44018052283135</v>
+        <v>3.621310310201458</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8116,7 +8116,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.659010149892568</v>
+        <v>3.614388074893878</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8124,22 +8124,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1406875972910801</v>
+        <v>0.1404467363543481</v>
       </c>
       <c r="C84">
-        <v>313.0632151871056</v>
+        <v>309.6212496629881</v>
       </c>
       <c r="D84">
-        <v>728.1532151871056</v>
+        <v>730.0062496629881</v>
       </c>
       <c r="E84">
-        <v>77.29000000000008</v>
+        <v>82.58500000000004</v>
       </c>
       <c r="F84">
-        <v>434.1900000000001</v>
+        <v>439.485</v>
       </c>
       <c r="G84">
         <v>19.1</v>
@@ -8160,28 +8160,28 @@
         <v>96.2</v>
       </c>
       <c r="M84">
-        <v>26.615847</v>
+        <v>26.9404305</v>
       </c>
       <c r="N84">
-        <v>69.584153</v>
+        <v>69.2595695</v>
       </c>
       <c r="O84">
-        <v>15.656434425</v>
+        <v>15.5834031375</v>
       </c>
       <c r="P84">
-        <v>53.927718575</v>
+        <v>53.6761663625</v>
       </c>
       <c r="Q84">
-        <v>75.227718575</v>
+        <v>74.9761663625</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5651747071726675</v>
+        <v>0.594208890319695</v>
       </c>
       <c r="T84">
-        <v>3.621310310201458</v>
+        <v>3.823749484320989</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.614388074893878</v>
+        <v>3.570841230618048</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8206,22 +8206,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1404467363543481</v>
+        <v>0.1402058754176162</v>
       </c>
       <c r="C85">
-        <v>309.6212496629881</v>
+        <v>306.1887395592598</v>
       </c>
       <c r="D85">
-        <v>730.0062496629881</v>
+        <v>731.8687395592598</v>
       </c>
       <c r="E85">
-        <v>82.58500000000004</v>
+        <v>87.88000000000005</v>
       </c>
       <c r="F85">
-        <v>439.485</v>
+        <v>444.78</v>
       </c>
       <c r="G85">
         <v>19.1</v>
@@ -8242,28 +8242,28 @@
         <v>96.2</v>
       </c>
       <c r="M85">
-        <v>26.9404305</v>
+        <v>27.265014</v>
       </c>
       <c r="N85">
-        <v>69.2595695</v>
+        <v>68.93498600000001</v>
       </c>
       <c r="O85">
-        <v>15.5834031375</v>
+        <v>15.51037185</v>
       </c>
       <c r="P85">
-        <v>53.6761663625</v>
+        <v>53.42461415000001</v>
       </c>
       <c r="Q85">
-        <v>74.9761663625</v>
+        <v>74.72461415000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.594208890319695</v>
+        <v>0.6268723463601015</v>
       </c>
       <c r="T85">
-        <v>3.823749484320989</v>
+        <v>4.051493555205465</v>
       </c>
       <c r="U85">
         <v>0.0613</v>
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.570841230618048</v>
+        <v>3.528331215967834</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8288,22 +8288,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1402058754176162</v>
+        <v>0.1418095144808842</v>
       </c>
       <c r="C86">
-        <v>306.1887395592601</v>
+        <v>288.6693958961571</v>
       </c>
       <c r="D86">
-        <v>731.86873955926</v>
+        <v>719.6443958961571</v>
       </c>
       <c r="E86">
-        <v>87.88</v>
+        <v>93.17500000000001</v>
       </c>
       <c r="F86">
-        <v>444.78</v>
+        <v>450.075</v>
       </c>
       <c r="G86">
         <v>19.1</v>
@@ -8324,45 +8324,45 @@
         <v>96.2</v>
       </c>
       <c r="M86">
-        <v>27.265014</v>
+        <v>28.8498075</v>
       </c>
       <c r="N86">
-        <v>68.93498600000001</v>
+        <v>67.35019250000001</v>
       </c>
       <c r="O86">
-        <v>15.51037185</v>
+        <v>15.1537933125</v>
       </c>
       <c r="P86">
-        <v>53.42461415000001</v>
+        <v>52.19639918750001</v>
       </c>
       <c r="Q86">
-        <v>74.72461415000001</v>
+        <v>73.4963991875</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6268723463601009</v>
+        <v>0.6638909298725613</v>
       </c>
       <c r="T86">
-        <v>4.051493555205461</v>
+        <v>4.309603502207865</v>
       </c>
       <c r="U86">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V86">
         <v>0.225</v>
       </c>
       <c r="W86">
-        <v>0.0475075</v>
+        <v>0.04967750000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y86">
-        <v>3.528331215967834</v>
+        <v>3.334510984172078</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8370,22 +8370,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1418095144808842</v>
+        <v>0.1415903535441522</v>
       </c>
       <c r="C87">
-        <v>288.6693958961571</v>
+        <v>285.0208867387432</v>
       </c>
       <c r="D87">
-        <v>719.6443958961571</v>
+        <v>721.2908867387432</v>
       </c>
       <c r="E87">
-        <v>93.17500000000001</v>
+        <v>98.47000000000003</v>
       </c>
       <c r="F87">
-        <v>450.075</v>
+        <v>455.37</v>
       </c>
       <c r="G87">
         <v>19.1</v>
@@ -8406,28 +8406,28 @@
         <v>96.2</v>
       </c>
       <c r="M87">
-        <v>28.8498075</v>
+        <v>29.189217</v>
       </c>
       <c r="N87">
-        <v>67.35019250000001</v>
+        <v>67.010783</v>
       </c>
       <c r="O87">
-        <v>15.1537933125</v>
+        <v>15.077426175</v>
       </c>
       <c r="P87">
-        <v>52.19639918750001</v>
+        <v>51.933356825</v>
       </c>
       <c r="Q87">
-        <v>73.4963991875</v>
+        <v>73.233356825</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6638909298725613</v>
+        <v>0.70619788245823</v>
       </c>
       <c r="T87">
-        <v>4.309603502207865</v>
+        <v>4.604586298782039</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.334510984172078</v>
+        <v>3.295737600635193</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8452,22 +8452,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1415903535441522</v>
+        <v>0.1413711926074202</v>
       </c>
       <c r="C88">
-        <v>285.0208867387432</v>
+        <v>281.3799289462445</v>
       </c>
       <c r="D88">
-        <v>721.2908867387432</v>
+        <v>722.9449289462445</v>
       </c>
       <c r="E88">
-        <v>98.47000000000003</v>
+        <v>103.765</v>
       </c>
       <c r="F88">
-        <v>455.37</v>
+        <v>460.665</v>
       </c>
       <c r="G88">
         <v>19.1</v>
@@ -8488,28 +8488,28 @@
         <v>96.2</v>
       </c>
       <c r="M88">
-        <v>29.189217</v>
+        <v>29.5286265</v>
       </c>
       <c r="N88">
-        <v>67.010783</v>
+        <v>66.6713735</v>
       </c>
       <c r="O88">
-        <v>15.077426175</v>
+        <v>15.0010590375</v>
       </c>
       <c r="P88">
-        <v>51.933356825</v>
+        <v>51.6703144625</v>
       </c>
       <c r="Q88">
-        <v>73.233356825</v>
+        <v>72.9703144625</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.70619788245823</v>
+        <v>0.7550135969801556</v>
       </c>
       <c r="T88">
-        <v>4.604586298782039</v>
+        <v>4.944951064059934</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.295737600635193</v>
+        <v>3.257855559248582</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8534,22 +8534,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1413711926074202</v>
+        <v>0.1411520316706882</v>
       </c>
       <c r="C89">
-        <v>281.3799289462445</v>
+        <v>277.7465745877418</v>
       </c>
       <c r="D89">
-        <v>722.9449289462445</v>
+        <v>724.6065745877418</v>
       </c>
       <c r="E89">
-        <v>103.765</v>
+        <v>109.06</v>
       </c>
       <c r="F89">
-        <v>460.665</v>
+        <v>465.96</v>
       </c>
       <c r="G89">
         <v>19.1</v>
@@ -8570,28 +8570,28 @@
         <v>96.2</v>
       </c>
       <c r="M89">
-        <v>29.5286265</v>
+        <v>29.868036</v>
       </c>
       <c r="N89">
-        <v>66.6713735</v>
+        <v>66.331964</v>
       </c>
       <c r="O89">
-        <v>15.0010590375</v>
+        <v>14.9246919</v>
       </c>
       <c r="P89">
-        <v>51.6703144625</v>
+        <v>51.4072721</v>
       </c>
       <c r="Q89">
-        <v>72.9703144625</v>
+        <v>72.7072721</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7550135969801556</v>
+        <v>0.8119652639224021</v>
       </c>
       <c r="T89">
-        <v>4.944951064059934</v>
+        <v>5.342043290217477</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.257855559248582</v>
+        <v>3.22083447334803</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8616,22 +8616,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1411520316706882</v>
+        <v>0.1409328707339563</v>
       </c>
       <c r="C90">
-        <v>277.7465745877418</v>
+        <v>274.1208762121287</v>
       </c>
       <c r="D90">
-        <v>724.6065745877418</v>
+        <v>726.2758762121287</v>
       </c>
       <c r="E90">
-        <v>109.06</v>
+        <v>114.355</v>
       </c>
       <c r="F90">
-        <v>465.96</v>
+        <v>471.255</v>
       </c>
       <c r="G90">
         <v>19.1</v>
@@ -8652,28 +8652,28 @@
         <v>96.2</v>
       </c>
       <c r="M90">
-        <v>29.868036</v>
+        <v>30.2074455</v>
       </c>
       <c r="N90">
-        <v>66.331964</v>
+        <v>65.9925545</v>
       </c>
       <c r="O90">
-        <v>14.9246919</v>
+        <v>14.8483247625</v>
       </c>
       <c r="P90">
-        <v>51.4072721</v>
+        <v>51.1442297375</v>
       </c>
       <c r="Q90">
-        <v>72.7072721</v>
+        <v>72.4442297375</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8119652639224021</v>
+        <v>0.8792717793996024</v>
       </c>
       <c r="T90">
-        <v>5.342043290217477</v>
+        <v>5.811334102949119</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.22083447334803</v>
+        <v>3.184645321962097</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8698,22 +8698,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1409328707339563</v>
+        <v>0.1407137097972243</v>
       </c>
       <c r="C91">
-        <v>274.1208762121287</v>
+        <v>270.5028868536529</v>
       </c>
       <c r="D91">
-        <v>726.2758762121287</v>
+        <v>727.9528868536529</v>
       </c>
       <c r="E91">
-        <v>114.355</v>
+        <v>119.65</v>
       </c>
       <c r="F91">
-        <v>471.255</v>
+        <v>476.55</v>
       </c>
       <c r="G91">
         <v>19.1</v>
@@ -8734,28 +8734,28 @@
         <v>96.2</v>
       </c>
       <c r="M91">
-        <v>30.2074455</v>
+        <v>30.546855</v>
       </c>
       <c r="N91">
-        <v>65.9925545</v>
+        <v>65.65314499999999</v>
       </c>
       <c r="O91">
-        <v>14.8483247625</v>
+        <v>14.771957625</v>
       </c>
       <c r="P91">
-        <v>51.1442297375</v>
+        <v>50.881187375</v>
       </c>
       <c r="Q91">
-        <v>72.4442297375</v>
+        <v>72.18118737499999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8792717793996024</v>
+        <v>0.960039597972243</v>
       </c>
       <c r="T91">
-        <v>5.811334102949119</v>
+        <v>6.37448307822709</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.184645321962097</v>
+        <v>3.149260373940296</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8780,22 +8780,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1407137097972243</v>
+        <v>0.1404945488604923</v>
       </c>
       <c r="C92">
-        <v>270.5028868536529</v>
+        <v>266.8926600375311</v>
       </c>
       <c r="D92">
-        <v>727.9528868536529</v>
+        <v>729.6376600375311</v>
       </c>
       <c r="E92">
-        <v>119.65</v>
+        <v>124.9450000000001</v>
       </c>
       <c r="F92">
-        <v>476.55</v>
+        <v>481.845</v>
       </c>
       <c r="G92">
         <v>19.1</v>
@@ -8816,28 +8816,28 @@
         <v>96.2</v>
       </c>
       <c r="M92">
-        <v>30.546855</v>
+        <v>30.8862645</v>
       </c>
       <c r="N92">
-        <v>65.65314499999999</v>
+        <v>65.31373550000001</v>
       </c>
       <c r="O92">
-        <v>14.771957625</v>
+        <v>14.6955904875</v>
       </c>
       <c r="P92">
-        <v>50.881187375</v>
+        <v>50.61814501250001</v>
       </c>
       <c r="Q92">
-        <v>72.18118737499999</v>
+        <v>71.91814501250001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.960039597972243</v>
+        <v>1.058755820672137</v>
       </c>
       <c r="T92">
-        <v>6.37448307822709</v>
+        <v>7.062776270233499</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.149260373940296</v>
+        <v>3.114653117083809</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8862,22 +8862,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1404945488604923</v>
+        <v>0.1402753879237603</v>
       </c>
       <c r="C93">
-        <v>266.8926600375311</v>
+        <v>263.290249785644</v>
       </c>
       <c r="D93">
-        <v>729.6376600375311</v>
+        <v>731.330249785644</v>
       </c>
       <c r="E93">
-        <v>124.9450000000001</v>
+        <v>130.2400000000001</v>
       </c>
       <c r="F93">
-        <v>481.845</v>
+        <v>487.14</v>
       </c>
       <c r="G93">
         <v>19.1</v>
@@ -8898,28 +8898,28 @@
         <v>96.2</v>
       </c>
       <c r="M93">
-        <v>30.8862645</v>
+        <v>31.22567400000001</v>
       </c>
       <c r="N93">
-        <v>65.31373550000001</v>
+        <v>64.97432599999999</v>
       </c>
       <c r="O93">
-        <v>14.6955904875</v>
+        <v>14.61922335</v>
       </c>
       <c r="P93">
-        <v>50.61814501250001</v>
+        <v>50.35510264999999</v>
       </c>
       <c r="Q93">
-        <v>71.91814501250001</v>
+        <v>71.65510264999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.058755820672137</v>
+        <v>1.182151099047005</v>
       </c>
       <c r="T93">
-        <v>7.062776270233499</v>
+        <v>7.923142760241511</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8936,7 +8936,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.114653117083809</v>
+        <v>3.080798191898115</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8944,22 +8944,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1402753879237603</v>
+        <v>0.1400562269870284</v>
       </c>
       <c r="C94">
-        <v>263.290249785644</v>
+        <v>259.6957106223113</v>
       </c>
       <c r="D94">
-        <v>731.330249785644</v>
+        <v>733.0307106223113</v>
       </c>
       <c r="E94">
-        <v>130.2400000000001</v>
+        <v>135.535</v>
       </c>
       <c r="F94">
-        <v>487.14</v>
+        <v>492.435</v>
       </c>
       <c r="G94">
         <v>19.1</v>
@@ -8980,28 +8980,28 @@
         <v>96.2</v>
       </c>
       <c r="M94">
-        <v>31.22567400000001</v>
+        <v>31.5650835</v>
       </c>
       <c r="N94">
-        <v>64.97432599999999</v>
+        <v>64.6349165</v>
       </c>
       <c r="O94">
-        <v>14.61922335</v>
+        <v>14.5428562125</v>
       </c>
       <c r="P94">
-        <v>50.35510264999999</v>
+        <v>50.0920602875</v>
       </c>
       <c r="Q94">
-        <v>71.65510264999999</v>
+        <v>71.3920602875</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.182151099047005</v>
+        <v>1.340802171243263</v>
       </c>
       <c r="T94">
-        <v>7.923142760241511</v>
+        <v>9.02932824739467</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.080798191898115</v>
+        <v>3.047671329619641</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9026,22 +9026,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1400562269870284</v>
+        <v>0.1398370660502964</v>
       </c>
       <c r="C95">
-        <v>259.6957106223113</v>
+        <v>256.1090975801454</v>
       </c>
       <c r="D95">
-        <v>733.0307106223113</v>
+        <v>734.7390975801454</v>
       </c>
       <c r="E95">
-        <v>135.535</v>
+        <v>140.83</v>
       </c>
       <c r="F95">
-        <v>492.435</v>
+        <v>497.73</v>
       </c>
       <c r="G95">
         <v>19.1</v>
@@ -9062,28 +9062,28 @@
         <v>96.2</v>
       </c>
       <c r="M95">
-        <v>31.5650835</v>
+        <v>31.904493</v>
       </c>
       <c r="N95">
-        <v>64.6349165</v>
+        <v>64.295507</v>
       </c>
       <c r="O95">
-        <v>14.5428562125</v>
+        <v>14.466489075</v>
       </c>
       <c r="P95">
-        <v>50.0920602875</v>
+        <v>49.829017925</v>
       </c>
       <c r="Q95">
-        <v>71.3920602875</v>
+        <v>71.129017925</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.340802171243263</v>
+        <v>1.552336934171607</v>
       </c>
       <c r="T95">
-        <v>9.02932824739467</v>
+        <v>10.50424223026555</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.047671329619641</v>
+        <v>3.015249294198155</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9108,22 +9108,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1398370660502964</v>
+        <v>0.1453606551135644</v>
       </c>
       <c r="C96">
-        <v>256.1090975801454</v>
+        <v>210.0510387280326</v>
       </c>
       <c r="D96">
-        <v>734.7390975801454</v>
+        <v>693.9760387280326</v>
       </c>
       <c r="E96">
-        <v>140.83</v>
+        <v>146.1250000000001</v>
       </c>
       <c r="F96">
-        <v>497.73</v>
+        <v>503.025</v>
       </c>
       <c r="G96">
         <v>19.1</v>
@@ -9144,45 +9144,45 @@
         <v>96.2</v>
       </c>
       <c r="M96">
-        <v>31.904493</v>
+        <v>36.1674975</v>
       </c>
       <c r="N96">
-        <v>64.295507</v>
+        <v>60.0325025</v>
       </c>
       <c r="O96">
-        <v>14.466489075</v>
+        <v>13.5073130625</v>
       </c>
       <c r="P96">
-        <v>49.829017925</v>
+        <v>46.5251894375</v>
       </c>
       <c r="Q96">
-        <v>71.129017925</v>
+        <v>67.8251894375</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.552336934171607</v>
+        <v>1.84848560227129</v>
       </c>
       <c r="T96">
-        <v>10.50424223026555</v>
+        <v>12.56912180628478</v>
       </c>
       <c r="U96">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V96">
         <v>0.225</v>
       </c>
       <c r="W96">
-        <v>0.04967750000000001</v>
+        <v>0.05572250000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y96">
-        <v>3.015249294198155</v>
+        <v>2.659846731170715</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9190,22 +9190,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1453606551135644</v>
+        <v>0.1452019441768324</v>
       </c>
       <c r="C97">
-        <v>210.0510387280326</v>
+        <v>205.8640813129961</v>
       </c>
       <c r="D97">
-        <v>693.9760387280326</v>
+        <v>695.0840813129961</v>
       </c>
       <c r="E97">
-        <v>146.1250000000001</v>
+        <v>151.4200000000001</v>
       </c>
       <c r="F97">
-        <v>503.025</v>
+        <v>508.3200000000001</v>
       </c>
       <c r="G97">
         <v>19.1</v>
@@ -9226,28 +9226,28 @@
         <v>96.2</v>
       </c>
       <c r="M97">
-        <v>36.1674975</v>
+        <v>36.54820800000001</v>
       </c>
       <c r="N97">
-        <v>60.0325025</v>
+        <v>59.65179199999999</v>
       </c>
       <c r="O97">
-        <v>13.5073130625</v>
+        <v>13.4216532</v>
       </c>
       <c r="P97">
-        <v>46.5251894375</v>
+        <v>46.23013879999999</v>
       </c>
       <c r="Q97">
-        <v>67.8251894375</v>
+        <v>67.53013879999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.84848560227129</v>
+        <v>2.292708604420814</v>
       </c>
       <c r="T97">
-        <v>12.56912180628478</v>
+        <v>15.66644117031363</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9264,7 +9264,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.659846731170715</v>
+        <v>2.632139994387686</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9272,22 +9272,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1452019441768324</v>
+        <v>0.1450432332401004</v>
       </c>
       <c r="C98">
-        <v>205.8640813129961</v>
+        <v>201.680667887224</v>
       </c>
       <c r="D98">
-        <v>695.0840813129961</v>
+        <v>696.195667887224</v>
       </c>
       <c r="E98">
-        <v>151.42</v>
+        <v>156.715</v>
       </c>
       <c r="F98">
-        <v>508.32</v>
+        <v>513.615</v>
       </c>
       <c r="G98">
         <v>19.1</v>
@@ -9308,28 +9308,28 @@
         <v>96.2</v>
       </c>
       <c r="M98">
-        <v>36.548208</v>
+        <v>36.9289185</v>
       </c>
       <c r="N98">
-        <v>59.651792</v>
+        <v>59.2710815</v>
       </c>
       <c r="O98">
-        <v>13.4216532</v>
+        <v>13.3359933375</v>
       </c>
       <c r="P98">
-        <v>46.2301388</v>
+        <v>45.9350881625</v>
       </c>
       <c r="Q98">
-        <v>67.5301388</v>
+        <v>67.23508816250001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.292708604420808</v>
+        <v>3.033080274670011</v>
       </c>
       <c r="T98">
-        <v>15.66644117031358</v>
+        <v>20.82864011036164</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.632139994387686</v>
+        <v>2.60500453052802</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9354,22 +9354,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1450432332401004</v>
+        <v>0.1448845223033685</v>
       </c>
       <c r="C99">
-        <v>201.680667887224</v>
+        <v>197.5008154807183</v>
       </c>
       <c r="D99">
-        <v>696.195667887224</v>
+        <v>697.3108154807182</v>
       </c>
       <c r="E99">
-        <v>156.715</v>
+        <v>162.01</v>
       </c>
       <c r="F99">
-        <v>513.615</v>
+        <v>518.91</v>
       </c>
       <c r="G99">
         <v>19.1</v>
@@ -9390,28 +9390,28 @@
         <v>96.2</v>
       </c>
       <c r="M99">
-        <v>36.9289185</v>
+        <v>37.309629</v>
       </c>
       <c r="N99">
-        <v>59.2710815</v>
+        <v>58.890371</v>
       </c>
       <c r="O99">
-        <v>13.3359933375</v>
+        <v>13.250333475</v>
       </c>
       <c r="P99">
-        <v>45.9350881625</v>
+        <v>45.640037525</v>
       </c>
       <c r="Q99">
-        <v>67.23508816250001</v>
+        <v>66.94003752499999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.033080274670011</v>
+        <v>4.513823615168418</v>
       </c>
       <c r="T99">
-        <v>20.82864011036164</v>
+        <v>31.15303799045775</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.60500453052802</v>
+        <v>2.57842285164508</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9436,22 +9436,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1448845223033685</v>
+        <v>0.1447258113666365</v>
       </c>
       <c r="C100">
-        <v>197.5008154807183</v>
+        <v>193.3245412327682</v>
       </c>
       <c r="D100">
-        <v>697.3108154807182</v>
+        <v>698.4295412327682</v>
       </c>
       <c r="E100">
-        <v>162.01</v>
+        <v>167.3050000000001</v>
       </c>
       <c r="F100">
-        <v>518.91</v>
+        <v>524.205</v>
       </c>
       <c r="G100">
         <v>19.1</v>
@@ -9472,28 +9472,28 @@
         <v>96.2</v>
       </c>
       <c r="M100">
-        <v>37.309629</v>
+        <v>37.69033950000001</v>
       </c>
       <c r="N100">
-        <v>58.890371</v>
+        <v>58.5096605</v>
       </c>
       <c r="O100">
-        <v>13.250333475</v>
+        <v>13.1646736125</v>
       </c>
       <c r="P100">
-        <v>45.640037525</v>
+        <v>45.3449868875</v>
       </c>
       <c r="Q100">
-        <v>66.94003752499999</v>
+        <v>66.6449868875</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.513823615168418</v>
+        <v>8.956053636663638</v>
       </c>
       <c r="T100">
-        <v>31.15303799045775</v>
+        <v>62.12623163074609</v>
       </c>
       <c r="U100">
         <v>0.07190000000000001</v>
@@ -9510,91 +9510,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.57842285164508</v>
+        <v>2.552378176375938</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1447258113666365</v>
-      </c>
-      <c r="C101">
-        <v>193.3245412327682</v>
-      </c>
-      <c r="D101">
-        <v>698.4295412327682</v>
-      </c>
-      <c r="E101">
-        <v>167.3050000000001</v>
-      </c>
-      <c r="F101">
-        <v>524.205</v>
-      </c>
-      <c r="G101">
-        <v>19.1</v>
-      </c>
-      <c r="H101">
-        <v>172.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>117.5</v>
-      </c>
-      <c r="K101">
-        <v>21.3</v>
-      </c>
-      <c r="L101">
-        <v>96.2</v>
-      </c>
-      <c r="M101">
-        <v>37.69033950000001</v>
-      </c>
-      <c r="N101">
-        <v>58.5096605</v>
-      </c>
-      <c r="O101">
-        <v>13.1646736125</v>
-      </c>
-      <c r="P101">
-        <v>45.3449868875</v>
-      </c>
-      <c r="Q101">
-        <v>66.6449868875</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.956053636663638</v>
-      </c>
-      <c r="T101">
-        <v>62.12623163074609</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.225</v>
-      </c>
-      <c r="W101">
-        <v>0.05572250000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.552378176375938</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
